--- a/public/Documentações/Backlog.xlsx
+++ b/public/Documentações/Backlog.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mathe\OneDrive\Área de Trabalho\ThermoChain\Documentações\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mathe\OneDrive\Área de Trabalho\ThermoChain\public\Documentações\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{100961CA-25F7-4948-986A-D9F783406DEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{691E1DE2-B26F-45D5-B6D4-F3BDFBEAD9F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{88668B19-0EBA-47FC-AF05-5256D7A9BC46}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{88668B19-0EBA-47FC-AF05-5256D7A9BC46}"/>
   </bookViews>
   <sheets>
     <sheet name="BackLog" sheetId="1" r:id="rId1"/>
     <sheet name="Sprint01" sheetId="2" r:id="rId2"/>
     <sheet name="Sprint02" sheetId="3" r:id="rId3"/>
+    <sheet name="Sprint03" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -60,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="120">
   <si>
     <t>Projeto no github</t>
   </si>
@@ -624,7 +625,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -632,7 +633,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -709,7 +709,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -725,7 +724,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -739,6 +737,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -867,10 +867,10 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>BackLog!$P$3:$P$117</c:f>
+              <c:f>BackLog!$P$3:$P$122</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="115"/>
+                <c:ptCount val="120"/>
                 <c:pt idx="0">
                   <c:v>306</c:v>
                 </c:pt>
@@ -1215,6 +1215,21 @@
                 </c:pt>
                 <c:pt idx="114">
                   <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1252,10 +1267,10 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>BackLog!$R$3:$R$87</c:f>
+              <c:f>BackLog!$R$3:$R$122</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="85"/>
+                <c:ptCount val="120"/>
                 <c:pt idx="0">
                   <c:v>306</c:v>
                 </c:pt>
@@ -1510,6 +1525,111 @@
                 </c:pt>
                 <c:pt idx="84">
                   <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>84</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>63</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2746,7 +2866,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{552007D4-E79E-4A61-AC31-FF3BEBBC1490}">
-  <dimension ref="A2:T118"/>
+  <dimension ref="A2:T122"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.5703125" customWidth="1"/>
@@ -2770,10 +2890,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="3">
         <v>3</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -2800,3692 +2920,3878 @@
       <c r="L2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="N2" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="O2" s="7" t="s">
+      <c r="O2" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="P2" s="8" t="s">
+      <c r="P2" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="Q2" s="7" t="s">
+      <c r="Q2" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="R2" s="9" t="s">
+      <c r="R2" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="S2" s="7" t="s">
+      <c r="S2" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="T2" s="10" t="s">
+      <c r="T2" s="9" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="3">
         <v>5</v>
       </c>
-      <c r="E3" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="F3" s="17" t="s">
+      <c r="E3" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="F3" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="H3" s="22" t="s">
+      <c r="H3" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="I3" s="22">
-        <v>3</v>
-      </c>
-      <c r="J3" s="20">
-        <v>3</v>
-      </c>
-      <c r="K3" s="23" t="s">
+      <c r="I3" s="21">
+        <v>3</v>
+      </c>
+      <c r="J3" s="19">
+        <v>3</v>
+      </c>
+      <c r="K3" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="N3" s="6">
-        <v>0</v>
-      </c>
-      <c r="O3" s="28">
-        <v>0</v>
-      </c>
-      <c r="P3" s="6">
+      <c r="N3" s="5">
+        <v>0</v>
+      </c>
+      <c r="O3" s="27">
+        <v>0</v>
+      </c>
+      <c r="P3" s="5">
         <f>B8</f>
         <v>306</v>
       </c>
-      <c r="Q3" s="6">
-        <v>0</v>
-      </c>
-      <c r="R3" s="6">
+      <c r="Q3" s="5">
+        <v>0</v>
+      </c>
+      <c r="R3" s="5">
         <f>B8</f>
         <v>306</v>
       </c>
-      <c r="S3" s="14">
+      <c r="S3" s="13">
         <v>46063</v>
       </c>
-      <c r="T3" s="11" t="s">
+      <c r="T3" s="10" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="3">
         <v>8</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="F4" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="G4" s="20" t="s">
+      <c r="G4" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="H4" s="24" t="s">
+      <c r="H4" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="I4" s="24">
+      <c r="I4" s="23">
         <v>8</v>
       </c>
-      <c r="J4" s="19">
+      <c r="J4" s="18">
         <v>1</v>
       </c>
-      <c r="K4" s="23" t="s">
+      <c r="K4" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="L4" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="N4" s="6" cm="1">
-        <f t="array" ref="N4:N117">_xlfn.SEQUENCE(114)</f>
+      <c r="N4" s="5" cm="1">
+        <f t="array" ref="N4:N122">_xlfn.SEQUENCE(119)</f>
         <v>1</v>
       </c>
-      <c r="O4" s="28">
+      <c r="O4" s="27">
         <f t="shared" ref="O4:O35" si="0">$B$10</f>
         <v>3</v>
       </c>
-      <c r="P4" s="6">
+      <c r="P4" s="5">
         <f>P3-$O$4</f>
         <v>303</v>
       </c>
-      <c r="Q4" s="6">
-        <v>0</v>
-      </c>
-      <c r="R4" s="6">
+      <c r="Q4" s="5">
+        <v>0</v>
+      </c>
+      <c r="R4" s="5">
         <f>R3-Q4</f>
         <v>306</v>
       </c>
-      <c r="S4" s="14">
+      <c r="S4" s="13">
         <f>S3+1</f>
         <v>46064</v>
       </c>
-      <c r="T4" s="12" t="s">
+      <c r="T4" s="11" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="3">
         <v>13</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="F5" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="G5" s="20" t="s">
+      <c r="G5" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="H5" s="26" t="s">
+      <c r="H5" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="I5" s="26">
+      <c r="I5" s="25">
         <v>13</v>
       </c>
-      <c r="J5" s="19">
+      <c r="J5" s="18">
         <v>1</v>
       </c>
-      <c r="K5" s="23" t="s">
+      <c r="K5" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="L5" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="N5" s="6">
+      <c r="N5" s="5">
         <v>2</v>
       </c>
-      <c r="O5" s="28">
+      <c r="O5" s="27">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="P5" s="6">
+      <c r="P5" s="5">
         <f t="shared" ref="P5:P68" si="1">P4-$O$4</f>
         <v>300</v>
       </c>
-      <c r="Q5" s="6">
-        <v>0</v>
-      </c>
-      <c r="R5" s="6">
+      <c r="Q5" s="5">
+        <v>0</v>
+      </c>
+      <c r="R5" s="5">
         <f>IF(Q5&lt;&gt;"",R4-Q5,R4)</f>
         <v>306</v>
       </c>
-      <c r="S5" s="14">
+      <c r="S5" s="13">
         <f t="shared" ref="S5:S68" si="2">S4+1</f>
         <v>46065</v>
       </c>
-      <c r="T5" s="13" t="s">
+      <c r="T5" s="12" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="3">
         <v>21</v>
       </c>
-      <c r="E6" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="F6" s="17" t="s">
+      <c r="E6" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="G6" s="20" t="s">
+      <c r="G6" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="H6" s="26" t="s">
+      <c r="H6" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="I6" s="26">
+      <c r="I6" s="25">
         <v>13</v>
       </c>
-      <c r="J6" s="19">
+      <c r="J6" s="18">
         <v>1</v>
       </c>
-      <c r="K6" s="23" t="s">
+      <c r="K6" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="L6" s="4" t="s">
+      <c r="L6" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="N6" s="6">
-        <v>3</v>
-      </c>
-      <c r="O6" s="28">
+      <c r="N6" s="5">
+        <v>3</v>
+      </c>
+      <c r="O6" s="27">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="P6" s="6">
+      <c r="P6" s="5">
         <f t="shared" si="1"/>
         <v>297</v>
       </c>
-      <c r="Q6" s="6">
+      <c r="Q6" s="5">
         <v>2</v>
       </c>
-      <c r="R6" s="6">
+      <c r="R6" s="5">
         <f t="shared" ref="R6:R69" si="3">IF(Q6&lt;&gt;"",R5-Q6,R5)</f>
         <v>304</v>
       </c>
-      <c r="S6" s="14">
+      <c r="S6" s="13">
         <f t="shared" si="2"/>
         <v>46066</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="F7" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="H7" s="26" t="s">
+      <c r="H7" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="I7" s="26">
+      <c r="I7" s="25">
         <v>13</v>
       </c>
-      <c r="J7" s="21">
+      <c r="J7" s="20">
         <v>2</v>
       </c>
-      <c r="K7" s="23" t="s">
+      <c r="K7" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="4" t="s">
+      <c r="L7" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="N7" s="6">
+      <c r="N7" s="5">
         <v>4</v>
       </c>
-      <c r="O7" s="28">
+      <c r="O7" s="27">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="P7" s="6">
+      <c r="P7" s="5">
         <f t="shared" si="1"/>
         <v>294</v>
       </c>
-      <c r="Q7" s="6">
-        <v>0</v>
-      </c>
-      <c r="R7" s="6">
+      <c r="Q7" s="5">
+        <v>0</v>
+      </c>
+      <c r="R7" s="5">
         <f t="shared" si="3"/>
         <v>304</v>
       </c>
-      <c r="S7" s="14">
+      <c r="S7" s="13">
         <f t="shared" si="2"/>
         <v>46067</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <f>SUM(I3:I41)</f>
         <v>306</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="F8" s="17" t="s">
+      <c r="F8" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="G8" s="20" t="s">
+      <c r="G8" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="H8" s="24" t="s">
+      <c r="H8" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="I8" s="24">
+      <c r="I8" s="23">
         <v>8</v>
       </c>
-      <c r="J8" s="19">
+      <c r="J8" s="18">
         <v>1</v>
       </c>
-      <c r="K8" s="23" t="s">
+      <c r="K8" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="L8" s="4" t="s">
+      <c r="L8" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="N8" s="6">
+      <c r="N8" s="5">
         <v>5</v>
       </c>
-      <c r="O8" s="28">
+      <c r="O8" s="27">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="P8" s="6">
+      <c r="P8" s="5">
         <f t="shared" si="1"/>
         <v>291</v>
       </c>
-      <c r="Q8" s="6">
-        <v>3</v>
-      </c>
-      <c r="R8" s="6">
+      <c r="Q8" s="5">
+        <v>3</v>
+      </c>
+      <c r="R8" s="5">
         <f t="shared" si="3"/>
         <v>301</v>
       </c>
-      <c r="S8" s="14">
+      <c r="S8" s="13">
         <f t="shared" si="2"/>
         <v>46068</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="B9" s="6">
-        <v>114</v>
-      </c>
-      <c r="E9" s="18" t="s">
+      <c r="B9" s="5">
+        <v>119</v>
+      </c>
+      <c r="E9" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="F9" s="17" t="s">
+      <c r="F9" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="G9" s="19" t="s">
+      <c r="G9" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="H9" s="23" t="s">
+      <c r="H9" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="I9" s="23">
+      <c r="I9" s="22">
         <v>5</v>
       </c>
-      <c r="J9" s="21">
+      <c r="J9" s="20">
         <v>2</v>
       </c>
-      <c r="K9" s="23" t="s">
+      <c r="K9" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="L9" s="4" t="s">
+      <c r="L9" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="N9" s="6">
+      <c r="N9" s="5">
         <v>6</v>
       </c>
-      <c r="O9" s="28">
+      <c r="O9" s="27">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="P9" s="6">
+      <c r="P9" s="5">
         <f t="shared" si="1"/>
         <v>288</v>
       </c>
-      <c r="Q9" s="6">
+      <c r="Q9" s="5">
         <v>1</v>
       </c>
-      <c r="R9" s="6">
+      <c r="R9" s="5">
         <f t="shared" si="3"/>
         <v>300</v>
       </c>
-      <c r="S9" s="14">
+      <c r="S9" s="13">
         <f t="shared" si="2"/>
         <v>46069</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="5">
         <f>ROUNDUP(B8/B9, 0)</f>
         <v>3</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="F10" s="17" t="s">
+      <c r="F10" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="G10" s="19" t="s">
+      <c r="G10" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="H10" s="22" t="s">
+      <c r="H10" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="I10" s="22">
-        <v>3</v>
-      </c>
-      <c r="J10" s="20">
-        <v>3</v>
-      </c>
-      <c r="K10" s="23" t="s">
+      <c r="I10" s="21">
+        <v>3</v>
+      </c>
+      <c r="J10" s="19">
+        <v>3</v>
+      </c>
+      <c r="K10" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="L10" s="4" t="s">
+      <c r="L10" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="N10" s="6">
+      <c r="N10" s="5">
         <v>7</v>
       </c>
-      <c r="O10" s="28">
+      <c r="O10" s="27">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="P10" s="6">
+      <c r="P10" s="5">
         <f t="shared" si="1"/>
         <v>285</v>
       </c>
-      <c r="Q10" s="6">
+      <c r="Q10" s="5">
         <v>4</v>
       </c>
-      <c r="R10" s="6">
+      <c r="R10" s="5">
         <f t="shared" si="3"/>
         <v>296</v>
       </c>
-      <c r="S10" s="14">
+      <c r="S10" s="13">
         <f t="shared" si="2"/>
         <v>46070</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A11" s="29" t="s">
+      <c r="A11" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="17" t="s">
+      <c r="F11" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="G11" s="20" t="s">
+      <c r="G11" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="H11" s="26" t="s">
+      <c r="H11" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="I11" s="26">
+      <c r="I11" s="25">
         <v>13</v>
       </c>
-      <c r="J11" s="19">
+      <c r="J11" s="18">
         <v>1</v>
       </c>
-      <c r="K11" s="23" t="s">
+      <c r="K11" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="L11" s="4" t="s">
+      <c r="L11" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="N11" s="6">
+      <c r="N11" s="5">
         <v>8</v>
       </c>
-      <c r="O11" s="28">
+      <c r="O11" s="27">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="P11" s="6">
+      <c r="P11" s="5">
         <f t="shared" si="1"/>
         <v>282</v>
       </c>
-      <c r="Q11" s="6">
-        <v>0</v>
-      </c>
-      <c r="R11" s="6">
+      <c r="Q11" s="5">
+        <v>0</v>
+      </c>
+      <c r="R11" s="5">
         <f t="shared" si="3"/>
         <v>296</v>
       </c>
-      <c r="S11" s="14">
+      <c r="S11" s="13">
         <f t="shared" si="2"/>
         <v>46071</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="F12" s="17" t="s">
+      <c r="F12" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="G12" s="20" t="s">
+      <c r="G12" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="H12" s="24" t="s">
+      <c r="H12" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="I12" s="24">
+      <c r="I12" s="23">
         <v>8</v>
       </c>
-      <c r="J12" s="19">
+      <c r="J12" s="18">
         <v>1</v>
       </c>
-      <c r="K12" s="23" t="s">
+      <c r="K12" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="L12" s="4" t="s">
+      <c r="L12" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="N12" s="6">
+      <c r="N12" s="5">
         <v>9</v>
       </c>
-      <c r="O12" s="28">
+      <c r="O12" s="27">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="P12" s="6">
+      <c r="P12" s="5">
         <f t="shared" si="1"/>
         <v>279</v>
       </c>
-      <c r="Q12" s="6">
+      <c r="Q12" s="5">
         <v>5</v>
       </c>
-      <c r="R12" s="6">
+      <c r="R12" s="5">
         <f t="shared" si="3"/>
         <v>291</v>
       </c>
-      <c r="S12" s="14">
+      <c r="S12" s="13">
         <f t="shared" si="2"/>
         <v>46072</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A13" s="5"/>
-      <c r="E13" s="18" t="s">
+      <c r="A13" s="4"/>
+      <c r="E13" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="17" t="s">
+      <c r="F13" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="G13" s="19" t="s">
+      <c r="G13" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="H13" s="23" t="s">
+      <c r="H13" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="I13" s="23">
+      <c r="I13" s="22">
         <v>5</v>
       </c>
-      <c r="J13" s="21">
+      <c r="J13" s="20">
         <v>2</v>
       </c>
-      <c r="K13" s="23" t="s">
+      <c r="K13" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="L13" s="4" t="s">
+      <c r="L13" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="N13" s="6">
+      <c r="N13" s="5">
         <v>10</v>
       </c>
-      <c r="O13" s="28">
+      <c r="O13" s="27">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="P13" s="6">
+      <c r="P13" s="5">
         <f t="shared" si="1"/>
         <v>276</v>
       </c>
-      <c r="Q13" s="6">
+      <c r="Q13" s="5">
         <v>2</v>
       </c>
-      <c r="R13" s="6">
+      <c r="R13" s="5">
         <f t="shared" si="3"/>
         <v>289</v>
       </c>
-      <c r="S13" s="14">
+      <c r="S13" s="13">
         <f t="shared" si="2"/>
         <v>46073</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A14" s="5"/>
-      <c r="E14" s="18" t="s">
+      <c r="A14" s="4"/>
+      <c r="E14" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="F14" s="17" t="s">
+      <c r="F14" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="G14" s="19" t="s">
+      <c r="G14" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="H14" s="23" t="s">
+      <c r="H14" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="I14" s="23">
+      <c r="I14" s="22">
         <v>5</v>
       </c>
-      <c r="J14" s="21">
+      <c r="J14" s="20">
         <v>2</v>
       </c>
-      <c r="K14" s="23" t="s">
+      <c r="K14" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="L14" s="4" t="s">
+      <c r="L14" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="N14" s="6">
+      <c r="N14" s="5">
         <v>11</v>
       </c>
-      <c r="O14" s="28">
+      <c r="O14" s="27">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="P14" s="6">
+      <c r="P14" s="5">
         <f t="shared" si="1"/>
         <v>273</v>
       </c>
-      <c r="Q14" s="6">
+      <c r="Q14" s="5">
         <v>6</v>
       </c>
-      <c r="R14" s="6">
+      <c r="R14" s="5">
         <f t="shared" si="3"/>
         <v>283</v>
       </c>
-      <c r="S14" s="14">
+      <c r="S14" s="13">
         <f t="shared" si="2"/>
         <v>46074</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="E15" s="18" t="s">
+      <c r="E15" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="F15" s="17" t="s">
+      <c r="F15" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="G15" s="19" t="s">
+      <c r="G15" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="H15" s="22" t="s">
+      <c r="H15" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="I15" s="22">
-        <v>3</v>
-      </c>
-      <c r="J15" s="20">
-        <v>3</v>
-      </c>
-      <c r="K15" s="23" t="s">
+      <c r="I15" s="21">
+        <v>3</v>
+      </c>
+      <c r="J15" s="19">
+        <v>3</v>
+      </c>
+      <c r="K15" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="L15" s="4" t="s">
+      <c r="L15" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="N15" s="6">
+      <c r="N15" s="5">
         <v>12</v>
       </c>
-      <c r="O15" s="28">
+      <c r="O15" s="27">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="P15" s="6">
+      <c r="P15" s="5">
         <f t="shared" si="1"/>
         <v>270</v>
       </c>
-      <c r="Q15" s="6">
-        <v>0</v>
-      </c>
-      <c r="R15" s="6">
+      <c r="Q15" s="5">
+        <v>0</v>
+      </c>
+      <c r="R15" s="5">
         <f t="shared" si="3"/>
         <v>283</v>
       </c>
-      <c r="S15" s="14">
+      <c r="S15" s="13">
         <f t="shared" si="2"/>
         <v>46075</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="E16" s="18" t="s">
+      <c r="E16" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F16" s="17" t="s">
+      <c r="F16" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="G16" s="19" t="s">
+      <c r="G16" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="H16" s="23" t="s">
+      <c r="H16" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="I16" s="23">
+      <c r="I16" s="22">
         <v>5</v>
       </c>
-      <c r="J16" s="20">
-        <v>3</v>
-      </c>
-      <c r="K16" s="23" t="s">
+      <c r="J16" s="19">
+        <v>3</v>
+      </c>
+      <c r="K16" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="L16" s="4" t="s">
+      <c r="L16" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="N16" s="6">
+      <c r="N16" s="5">
         <v>13</v>
       </c>
-      <c r="O16" s="28">
+      <c r="O16" s="27">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="P16" s="6">
+      <c r="P16" s="5">
         <f t="shared" si="1"/>
         <v>267</v>
       </c>
-      <c r="Q16" s="6">
+      <c r="Q16" s="5">
         <v>7</v>
       </c>
-      <c r="R16" s="6">
+      <c r="R16" s="5">
         <f t="shared" si="3"/>
         <v>276</v>
       </c>
-      <c r="S16" s="14">
+      <c r="S16" s="13">
         <f t="shared" si="2"/>
         <v>46076</v>
       </c>
     </row>
     <row r="17" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E17" s="18" t="s">
+      <c r="E17" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="F17" s="17" t="s">
+      <c r="F17" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="G17" s="20" t="s">
+      <c r="G17" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="H17" s="22" t="s">
+      <c r="H17" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="I17" s="22">
-        <v>3</v>
-      </c>
-      <c r="J17" s="19">
+      <c r="I17" s="21">
+        <v>3</v>
+      </c>
+      <c r="J17" s="18">
         <v>1</v>
       </c>
-      <c r="K17" s="23" t="s">
+      <c r="K17" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="L17" s="4" t="s">
+      <c r="L17" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="N17" s="6">
+      <c r="N17" s="5">
         <v>14</v>
       </c>
-      <c r="O17" s="28">
+      <c r="O17" s="27">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="P17" s="6">
+      <c r="P17" s="5">
         <f t="shared" si="1"/>
         <v>264</v>
       </c>
-      <c r="Q17" s="6">
-        <v>3</v>
-      </c>
-      <c r="R17" s="6">
+      <c r="Q17" s="5">
+        <v>3</v>
+      </c>
+      <c r="R17" s="5">
         <f t="shared" si="3"/>
         <v>273</v>
       </c>
-      <c r="S17" s="14">
+      <c r="S17" s="13">
         <f t="shared" si="2"/>
         <v>46077</v>
       </c>
     </row>
     <row r="18" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E18" s="18" t="s">
+      <c r="E18" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="F18" s="17" t="s">
+      <c r="F18" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="G18" s="20" t="s">
+      <c r="G18" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="H18" s="23" t="s">
+      <c r="H18" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="I18" s="23">
+      <c r="I18" s="22">
         <v>5</v>
       </c>
-      <c r="J18" s="19">
+      <c r="J18" s="18">
         <v>1</v>
       </c>
-      <c r="K18" s="23" t="s">
+      <c r="K18" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="L18" s="4" t="s">
+      <c r="L18" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="N18" s="6">
+      <c r="N18" s="5">
         <v>15</v>
       </c>
-      <c r="O18" s="28">
+      <c r="O18" s="27">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="P18" s="6">
+      <c r="P18" s="5">
         <f t="shared" si="1"/>
         <v>261</v>
       </c>
-      <c r="Q18" s="6">
+      <c r="Q18" s="5">
         <v>8</v>
       </c>
-      <c r="R18" s="6">
+      <c r="R18" s="5">
         <f t="shared" si="3"/>
         <v>265</v>
       </c>
-      <c r="S18" s="14">
+      <c r="S18" s="13">
         <f t="shared" si="2"/>
         <v>46078</v>
       </c>
     </row>
     <row r="19" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E19" s="18" t="s">
+      <c r="E19" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="F19" s="17" t="s">
+      <c r="F19" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="G19" s="19" t="s">
+      <c r="G19" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="H19" s="22" t="s">
+      <c r="H19" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="I19" s="22">
-        <v>3</v>
-      </c>
-      <c r="J19" s="21">
+      <c r="I19" s="21">
+        <v>3</v>
+      </c>
+      <c r="J19" s="20">
         <v>2</v>
       </c>
-      <c r="K19" s="19" t="s">
+      <c r="K19" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="L19" s="4" t="s">
+      <c r="L19" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="N19" s="6">
+      <c r="N19" s="5">
         <v>16</v>
       </c>
-      <c r="O19" s="28">
+      <c r="O19" s="27">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="P19" s="6">
+      <c r="P19" s="5">
         <f t="shared" si="1"/>
         <v>258</v>
       </c>
-      <c r="Q19" s="6">
-        <v>0</v>
-      </c>
-      <c r="R19" s="6">
+      <c r="Q19" s="5">
+        <v>0</v>
+      </c>
+      <c r="R19" s="5">
         <f t="shared" si="3"/>
         <v>265</v>
       </c>
-      <c r="S19" s="14">
+      <c r="S19" s="13">
         <f t="shared" si="2"/>
         <v>46079</v>
       </c>
     </row>
     <row r="20" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E20" s="18" t="s">
+      <c r="E20" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="F20" s="17" t="s">
+      <c r="F20" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="G20" s="19" t="s">
+      <c r="G20" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="H20" s="22" t="s">
+      <c r="H20" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="I20" s="22">
-        <v>3</v>
-      </c>
-      <c r="J20" s="21">
+      <c r="I20" s="21">
+        <v>3</v>
+      </c>
+      <c r="J20" s="20">
         <v>2</v>
       </c>
-      <c r="K20" s="19" t="s">
+      <c r="K20" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="L20" s="4" t="s">
+      <c r="L20" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="N20" s="6">
+      <c r="N20" s="5">
         <v>17</v>
       </c>
-      <c r="O20" s="28">
+      <c r="O20" s="27">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="P20" s="6">
+      <c r="P20" s="5">
         <f t="shared" si="1"/>
         <v>255</v>
       </c>
-      <c r="Q20" s="6">
+      <c r="Q20" s="5">
         <v>9</v>
       </c>
-      <c r="R20" s="6">
+      <c r="R20" s="5">
         <f t="shared" si="3"/>
         <v>256</v>
       </c>
-      <c r="S20" s="14">
+      <c r="S20" s="13">
         <f t="shared" si="2"/>
         <v>46080</v>
       </c>
     </row>
     <row r="21" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E21" s="18" t="s">
+      <c r="E21" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="F21" s="17" t="s">
+      <c r="F21" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="G21" s="21" t="s">
+      <c r="G21" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="H21" s="24" t="s">
+      <c r="H21" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="I21" s="24">
+      <c r="I21" s="23">
         <v>8</v>
       </c>
-      <c r="J21" s="20">
-        <v>3</v>
-      </c>
-      <c r="K21" s="19" t="s">
+      <c r="J21" s="19">
+        <v>3</v>
+      </c>
+      <c r="K21" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="L21" s="4" t="s">
+      <c r="L21" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="N21" s="6">
+      <c r="N21" s="5">
         <v>18</v>
       </c>
-      <c r="O21" s="28">
+      <c r="O21" s="27">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="P21" s="6">
+      <c r="P21" s="5">
         <f t="shared" si="1"/>
         <v>252</v>
       </c>
-      <c r="Q21" s="6">
+      <c r="Q21" s="5">
         <v>4</v>
       </c>
-      <c r="R21" s="6">
+      <c r="R21" s="5">
         <f t="shared" si="3"/>
         <v>252</v>
       </c>
-      <c r="S21" s="14">
+      <c r="S21" s="13">
         <f t="shared" si="2"/>
         <v>46081</v>
       </c>
     </row>
     <row r="22" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E22" s="18" t="s">
+      <c r="E22" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="F22" s="17" t="s">
+      <c r="F22" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="G22" s="19" t="s">
+      <c r="G22" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="H22" s="26" t="s">
+      <c r="H22" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="I22" s="26">
+      <c r="I22" s="25">
         <v>13</v>
       </c>
-      <c r="J22" s="19">
+      <c r="J22" s="18">
         <v>1</v>
       </c>
-      <c r="K22" s="19" t="s">
+      <c r="K22" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="L22" s="4" t="s">
+      <c r="L22" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="N22" s="6">
+      <c r="N22" s="5">
         <v>19</v>
       </c>
-      <c r="O22" s="28">
+      <c r="O22" s="27">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="P22" s="6">
+      <c r="P22" s="5">
         <f t="shared" si="1"/>
         <v>249</v>
       </c>
-      <c r="Q22" s="6">
+      <c r="Q22" s="5">
         <v>10</v>
       </c>
-      <c r="R22" s="6">
+      <c r="R22" s="5">
         <f t="shared" si="3"/>
         <v>242</v>
       </c>
-      <c r="S22" s="14">
+      <c r="S22" s="13">
         <f t="shared" si="2"/>
         <v>46082</v>
       </c>
     </row>
     <row r="23" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E23" s="18" t="s">
+      <c r="E23" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="F23" s="43" t="s">
+      <c r="F23" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="G23" s="19" t="s">
+      <c r="G23" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="H23" s="26" t="s">
+      <c r="H23" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="I23" s="26">
+      <c r="I23" s="25">
         <v>13</v>
       </c>
-      <c r="J23" s="19">
+      <c r="J23" s="18">
         <v>1</v>
       </c>
-      <c r="K23" s="19" t="s">
+      <c r="K23" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="L23" s="4" t="s">
+      <c r="L23" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="N23" s="6">
+      <c r="N23" s="5">
         <v>20</v>
       </c>
-      <c r="O23" s="28">
+      <c r="O23" s="27">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="P23" s="6">
+      <c r="P23" s="5">
         <f t="shared" si="1"/>
         <v>246</v>
       </c>
-      <c r="Q23" s="6">
-        <v>0</v>
-      </c>
-      <c r="R23" s="6">
+      <c r="Q23" s="5">
+        <v>0</v>
+      </c>
+      <c r="R23" s="5">
         <f t="shared" si="3"/>
         <v>242</v>
       </c>
-      <c r="S23" s="14">
+      <c r="S23" s="13">
         <f t="shared" si="2"/>
         <v>46083</v>
       </c>
     </row>
     <row r="24" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E24" s="18" t="s">
+      <c r="E24" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="F24" s="17" t="s">
+      <c r="F24" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="G24" s="20" t="s">
+      <c r="G24" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="H24" s="24" t="s">
+      <c r="H24" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="I24" s="24">
+      <c r="I24" s="23">
         <v>8</v>
       </c>
-      <c r="J24" s="21">
+      <c r="J24" s="20">
         <v>2</v>
       </c>
-      <c r="K24" s="19" t="s">
+      <c r="K24" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="L24" s="4" t="s">
+      <c r="L24" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="N24" s="6">
+      <c r="N24" s="5">
         <v>21</v>
       </c>
-      <c r="O24" s="28">
+      <c r="O24" s="27">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="P24" s="6">
+      <c r="P24" s="5">
         <f t="shared" si="1"/>
         <v>243</v>
       </c>
-      <c r="Q24" s="6">
+      <c r="Q24" s="5">
         <v>8</v>
       </c>
-      <c r="R24" s="6">
+      <c r="R24" s="5">
         <f t="shared" si="3"/>
         <v>234</v>
       </c>
-      <c r="S24" s="14">
+      <c r="S24" s="13">
         <f t="shared" si="2"/>
         <v>46084</v>
       </c>
     </row>
     <row r="25" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E25" s="18" t="s">
+      <c r="E25" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="F25" s="43" t="s">
+      <c r="F25" s="40" t="s">
         <v>74</v>
       </c>
-      <c r="G25" s="20" t="s">
+      <c r="G25" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="H25" s="24" t="s">
+      <c r="H25" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="I25" s="24">
+      <c r="I25" s="23">
         <v>8</v>
       </c>
-      <c r="J25" s="21">
+      <c r="J25" s="20">
         <v>2</v>
       </c>
-      <c r="K25" s="19" t="s">
+      <c r="K25" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="L25" s="4" t="s">
+      <c r="L25" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="N25" s="6">
+      <c r="N25" s="5">
         <v>22</v>
       </c>
-      <c r="O25" s="28">
+      <c r="O25" s="27">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="P25" s="6">
+      <c r="P25" s="5">
         <f t="shared" si="1"/>
         <v>240</v>
       </c>
-      <c r="Q25" s="6">
+      <c r="Q25" s="5">
         <v>6</v>
       </c>
-      <c r="R25" s="6">
+      <c r="R25" s="5">
         <f t="shared" si="3"/>
         <v>228</v>
       </c>
-      <c r="S25" s="14">
+      <c r="S25" s="13">
         <f t="shared" si="2"/>
         <v>46085</v>
       </c>
     </row>
     <row r="26" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E26" s="18" t="s">
+      <c r="E26" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="F26" s="43" t="s">
+      <c r="F26" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="G26" s="20" t="s">
+      <c r="G26" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="H26" s="22" t="s">
+      <c r="H26" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="I26" s="22">
-        <v>3</v>
-      </c>
-      <c r="J26" s="20">
-        <v>3</v>
-      </c>
-      <c r="K26" s="19" t="s">
+      <c r="I26" s="21">
+        <v>3</v>
+      </c>
+      <c r="J26" s="19">
+        <v>3</v>
+      </c>
+      <c r="K26" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="L26" s="4" t="s">
+      <c r="L26" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="N26" s="6">
+      <c r="N26" s="5">
         <v>23</v>
       </c>
-      <c r="O26" s="28">
+      <c r="O26" s="27">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="P26" s="6">
+      <c r="P26" s="5">
         <f t="shared" si="1"/>
         <v>237</v>
       </c>
-      <c r="Q26" s="6">
+      <c r="Q26" s="5">
         <v>9</v>
       </c>
-      <c r="R26" s="6">
+      <c r="R26" s="5">
         <f t="shared" si="3"/>
         <v>219</v>
       </c>
-      <c r="S26" s="14">
+      <c r="S26" s="13">
         <f t="shared" si="2"/>
         <v>46086</v>
       </c>
     </row>
     <row r="27" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E27" s="18" t="s">
+      <c r="E27" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="F27" s="17" t="s">
+      <c r="F27" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="G27" s="20" t="s">
+      <c r="G27" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="H27" s="23" t="s">
+      <c r="H27" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="I27" s="23">
+      <c r="I27" s="22">
         <v>5</v>
       </c>
-      <c r="J27" s="20">
-        <v>3</v>
-      </c>
-      <c r="K27" s="19" t="s">
+      <c r="J27" s="19">
+        <v>3</v>
+      </c>
+      <c r="K27" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="L27" s="4" t="s">
+      <c r="L27" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="N27" s="6">
+      <c r="N27" s="5">
         <v>24</v>
       </c>
-      <c r="O27" s="28">
+      <c r="O27" s="27">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="P27" s="6">
+      <c r="P27" s="5">
         <f t="shared" si="1"/>
         <v>234</v>
       </c>
-      <c r="Q27" s="6">
-        <v>0</v>
-      </c>
-      <c r="R27" s="6">
+      <c r="Q27" s="5">
+        <v>0</v>
+      </c>
+      <c r="R27" s="5">
         <f t="shared" si="3"/>
         <v>219</v>
       </c>
-      <c r="S27" s="14">
+      <c r="S27" s="13">
         <f t="shared" si="2"/>
         <v>46087</v>
       </c>
     </row>
     <row r="28" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E28" s="18" t="s">
+      <c r="E28" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="F28" s="17" t="s">
+      <c r="F28" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="G28" s="20" t="s">
+      <c r="G28" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="H28" s="24" t="s">
+      <c r="H28" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="I28" s="24">
+      <c r="I28" s="23">
         <v>8</v>
       </c>
-      <c r="J28" s="19">
+      <c r="J28" s="18">
         <v>1</v>
       </c>
-      <c r="K28" s="19" t="s">
+      <c r="K28" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="L28" s="4" t="s">
+      <c r="L28" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="N28" s="6">
+      <c r="N28" s="5">
         <v>25</v>
       </c>
-      <c r="O28" s="28">
+      <c r="O28" s="27">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="P28" s="6">
+      <c r="P28" s="5">
         <f t="shared" si="1"/>
         <v>231</v>
       </c>
-      <c r="Q28" s="6">
+      <c r="Q28" s="5">
         <v>7</v>
       </c>
-      <c r="R28" s="6">
+      <c r="R28" s="5">
         <f t="shared" si="3"/>
         <v>212</v>
       </c>
-      <c r="S28" s="14">
+      <c r="S28" s="13">
         <f t="shared" si="2"/>
         <v>46088</v>
       </c>
     </row>
     <row r="29" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E29" s="18" t="s">
+      <c r="E29" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="F29" s="17" t="s">
+      <c r="F29" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="G29" s="19" t="s">
+      <c r="G29" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="H29" s="24" t="s">
+      <c r="H29" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="I29" s="24">
+      <c r="I29" s="23">
         <v>8</v>
       </c>
-      <c r="J29" s="21">
+      <c r="J29" s="20">
         <v>2</v>
       </c>
-      <c r="K29" s="19" t="s">
+      <c r="K29" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="L29" s="4" t="s">
+      <c r="L29" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="N29" s="6">
+      <c r="N29" s="5">
         <v>26</v>
       </c>
-      <c r="O29" s="28">
+      <c r="O29" s="27">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="P29" s="6">
+      <c r="P29" s="5">
         <f t="shared" si="1"/>
         <v>228</v>
       </c>
-      <c r="Q29" s="6">
+      <c r="Q29" s="5">
         <v>5</v>
       </c>
-      <c r="R29" s="6">
+      <c r="R29" s="5">
         <f t="shared" si="3"/>
         <v>207</v>
       </c>
-      <c r="S29" s="14">
+      <c r="S29" s="13">
         <f t="shared" si="2"/>
         <v>46089</v>
       </c>
     </row>
     <row r="30" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E30" s="18" t="s">
+      <c r="E30" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="F30" s="17" t="s">
+      <c r="F30" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="G30" s="20" t="s">
+      <c r="G30" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="H30" s="23" t="s">
+      <c r="H30" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="I30" s="23">
+      <c r="I30" s="22">
         <v>5</v>
       </c>
-      <c r="J30" s="19">
+      <c r="J30" s="18">
         <v>1</v>
       </c>
-      <c r="K30" s="19" t="s">
+      <c r="K30" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="L30" s="4" t="s">
+      <c r="L30" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="N30" s="6">
+      <c r="N30" s="5">
         <v>27</v>
       </c>
-      <c r="O30" s="28">
+      <c r="O30" s="27">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="P30" s="6">
+      <c r="P30" s="5">
         <f t="shared" si="1"/>
         <v>225</v>
       </c>
-      <c r="Q30" s="6">
+      <c r="Q30" s="5">
         <v>6</v>
       </c>
-      <c r="R30" s="6">
+      <c r="R30" s="5">
         <f t="shared" si="3"/>
         <v>201</v>
       </c>
-      <c r="S30" s="14">
+      <c r="S30" s="13">
         <f t="shared" si="2"/>
         <v>46090</v>
       </c>
     </row>
     <row r="31" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E31" s="18" t="s">
+      <c r="E31" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="F31" s="17" t="s">
+      <c r="F31" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="G31" s="20" t="s">
+      <c r="G31" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="H31" s="23" t="s">
+      <c r="H31" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="I31" s="23">
+      <c r="I31" s="22">
         <v>5</v>
       </c>
-      <c r="J31" s="19">
+      <c r="J31" s="18">
         <v>1</v>
       </c>
-      <c r="K31" s="19" t="s">
+      <c r="K31" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="L31" s="4" t="s">
+      <c r="L31" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="N31" s="6">
+      <c r="N31" s="5">
         <v>28</v>
       </c>
-      <c r="O31" s="28">
+      <c r="O31" s="27">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="P31" s="6">
+      <c r="P31" s="5">
         <f t="shared" si="1"/>
         <v>222</v>
       </c>
-      <c r="Q31" s="6">
-        <v>0</v>
-      </c>
-      <c r="R31" s="6">
+      <c r="Q31" s="5">
+        <v>0</v>
+      </c>
+      <c r="R31" s="5">
         <f t="shared" si="3"/>
         <v>201</v>
       </c>
-      <c r="S31" s="14">
+      <c r="S31" s="13">
         <f t="shared" si="2"/>
         <v>46091</v>
       </c>
     </row>
     <row r="32" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E32" s="18" t="s">
+      <c r="E32" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="F32" s="17" t="s">
+      <c r="F32" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="G32" s="20" t="s">
+      <c r="G32" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="H32" s="23" t="s">
+      <c r="H32" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="I32" s="23">
+      <c r="I32" s="22">
         <v>5</v>
       </c>
-      <c r="J32" s="20">
-        <v>3</v>
-      </c>
-      <c r="K32" s="19" t="s">
+      <c r="J32" s="19">
+        <v>3</v>
+      </c>
+      <c r="K32" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="L32" s="4" t="s">
+      <c r="L32" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="N32" s="6">
+      <c r="N32" s="5">
         <v>29</v>
       </c>
-      <c r="O32" s="28">
+      <c r="O32" s="27">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="P32" s="6">
+      <c r="P32" s="5">
         <f t="shared" si="1"/>
         <v>219</v>
       </c>
-      <c r="Q32" s="6">
+      <c r="Q32" s="5">
         <v>4</v>
       </c>
-      <c r="R32" s="6">
+      <c r="R32" s="5">
         <f t="shared" si="3"/>
         <v>197</v>
       </c>
-      <c r="S32" s="14">
+      <c r="S32" s="13">
         <f t="shared" si="2"/>
         <v>46092</v>
       </c>
     </row>
     <row r="33" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E33" s="18" t="s">
+      <c r="E33" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="F33" s="43" t="s">
+      <c r="F33" s="40" t="s">
         <v>86</v>
       </c>
-      <c r="G33" s="20" t="s">
+      <c r="G33" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="H33" s="22" t="s">
+      <c r="H33" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="I33" s="22">
-        <v>3</v>
-      </c>
-      <c r="J33" s="20">
-        <v>3</v>
-      </c>
-      <c r="K33" s="19" t="s">
+      <c r="I33" s="21">
+        <v>3</v>
+      </c>
+      <c r="J33" s="19">
+        <v>3</v>
+      </c>
+      <c r="K33" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="L33" s="4" t="s">
+      <c r="L33" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="N33" s="6">
+      <c r="N33" s="5">
         <v>30</v>
       </c>
-      <c r="O33" s="28">
+      <c r="O33" s="27">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="P33" s="6">
+      <c r="P33" s="5">
         <f t="shared" si="1"/>
         <v>216</v>
       </c>
-      <c r="Q33" s="6">
-        <v>3</v>
-      </c>
-      <c r="R33" s="6">
+      <c r="Q33" s="5">
+        <v>3</v>
+      </c>
+      <c r="R33" s="5">
         <f t="shared" si="3"/>
         <v>194</v>
       </c>
-      <c r="S33" s="14">
+      <c r="S33" s="13">
         <f t="shared" si="2"/>
         <v>46093</v>
       </c>
     </row>
     <row r="34" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E34" s="18" t="s">
+      <c r="E34" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="F34" s="43" t="s">
+      <c r="F34" s="40" t="s">
         <v>87</v>
       </c>
-      <c r="G34" s="19" t="s">
+      <c r="G34" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="H34" s="22" t="s">
+      <c r="H34" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="I34" s="22">
-        <v>3</v>
-      </c>
-      <c r="J34" s="19">
+      <c r="I34" s="21">
+        <v>3</v>
+      </c>
+      <c r="J34" s="18">
         <v>1</v>
       </c>
-      <c r="K34" s="19" t="s">
+      <c r="K34" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="L34" s="4" t="s">
+      <c r="L34" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="N34" s="6">
+      <c r="N34" s="5">
         <v>31</v>
       </c>
-      <c r="O34" s="28">
+      <c r="O34" s="27">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="P34" s="6">
+      <c r="P34" s="5">
         <f t="shared" si="1"/>
         <v>213</v>
       </c>
-      <c r="Q34" s="6">
+      <c r="Q34" s="5">
         <v>1</v>
       </c>
-      <c r="R34" s="6">
+      <c r="R34" s="5">
         <f t="shared" si="3"/>
         <v>193</v>
       </c>
-      <c r="S34" s="14">
+      <c r="S34" s="13">
         <f t="shared" si="2"/>
         <v>46094</v>
       </c>
     </row>
     <row r="35" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E35" s="18" t="s">
+      <c r="E35" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="F35" s="3" t="s">
+      <c r="F35" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="G35" s="19" t="s">
+      <c r="G35" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="H35" s="26" t="s">
+      <c r="H35" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="I35" s="26">
+      <c r="I35" s="25">
         <v>13</v>
       </c>
-      <c r="J35" s="21">
+      <c r="J35" s="20">
         <v>2</v>
       </c>
-      <c r="K35" s="27" t="s">
+      <c r="K35" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="L35" s="4"/>
-      <c r="N35" s="6">
+      <c r="L35" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="N35" s="5">
         <v>32</v>
       </c>
-      <c r="O35" s="28">
+      <c r="O35" s="27">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="P35" s="6">
+      <c r="P35" s="5">
         <f t="shared" si="1"/>
         <v>210</v>
       </c>
-      <c r="Q35" s="6">
-        <v>0</v>
-      </c>
-      <c r="R35" s="6">
+      <c r="Q35" s="5">
+        <v>0</v>
+      </c>
+      <c r="R35" s="5">
         <f t="shared" si="3"/>
         <v>193</v>
       </c>
-      <c r="S35" s="14">
+      <c r="S35" s="13">
         <f t="shared" si="2"/>
         <v>46095</v>
       </c>
     </row>
     <row r="36" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E36" s="18" t="s">
+      <c r="E36" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="F36" s="3" t="s">
+      <c r="F36" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="G36" s="20" t="s">
+      <c r="G36" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="H36" s="25" t="s">
+      <c r="H36" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="I36" s="25">
+      <c r="I36" s="24">
         <v>21</v>
       </c>
-      <c r="J36" s="20">
-        <v>3</v>
-      </c>
-      <c r="K36" s="27" t="s">
+      <c r="J36" s="19">
+        <v>3</v>
+      </c>
+      <c r="K36" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="L36" s="4"/>
-      <c r="N36" s="6">
+      <c r="L36" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="N36" s="5">
         <v>33</v>
       </c>
-      <c r="O36" s="28">
+      <c r="O36" s="27">
         <f t="shared" ref="O36:O67" si="4">$B$10</f>
         <v>3</v>
       </c>
-      <c r="P36" s="6">
+      <c r="P36" s="5">
         <f t="shared" si="1"/>
         <v>207</v>
       </c>
-      <c r="Q36" s="6">
-        <v>0</v>
-      </c>
-      <c r="R36" s="6">
+      <c r="Q36" s="5">
+        <v>0</v>
+      </c>
+      <c r="R36" s="5">
         <f t="shared" si="3"/>
         <v>193</v>
       </c>
-      <c r="S36" s="14">
+      <c r="S36" s="13">
         <f t="shared" si="2"/>
         <v>46096</v>
       </c>
     </row>
     <row r="37" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E37" s="18" t="s">
+      <c r="E37" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="F37" s="3" t="s">
+      <c r="F37" s="40" t="s">
         <v>97</v>
       </c>
-      <c r="G37" s="19" t="s">
+      <c r="G37" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="H37" s="24" t="s">
+      <c r="H37" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="I37" s="24">
+      <c r="I37" s="23">
         <v>8</v>
       </c>
-      <c r="J37" s="21">
+      <c r="J37" s="20">
         <v>2</v>
       </c>
-      <c r="K37" s="27" t="s">
+      <c r="K37" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="L37" s="4"/>
-      <c r="N37" s="6">
+      <c r="L37" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="N37" s="5">
         <v>34</v>
       </c>
-      <c r="O37" s="28">
+      <c r="O37" s="27">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="P37" s="6">
+      <c r="P37" s="5">
         <f t="shared" si="1"/>
         <v>204</v>
       </c>
-      <c r="Q37" s="6">
-        <v>0</v>
-      </c>
-      <c r="R37" s="6">
+      <c r="Q37" s="5">
+        <v>0</v>
+      </c>
+      <c r="R37" s="5">
         <f t="shared" si="3"/>
         <v>193</v>
       </c>
-      <c r="S37" s="14">
+      <c r="S37" s="13">
         <f t="shared" si="2"/>
         <v>46097</v>
       </c>
     </row>
     <row r="38" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E38" s="18" t="s">
+      <c r="E38" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="F38" s="3" t="s">
+      <c r="F38" s="40" t="s">
         <v>98</v>
       </c>
-      <c r="G38" s="20" t="s">
+      <c r="G38" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="H38" s="24" t="s">
+      <c r="H38" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="I38" s="24">
+      <c r="I38" s="23">
         <v>8</v>
       </c>
-      <c r="J38" s="19">
+      <c r="J38" s="18">
         <v>1</v>
       </c>
-      <c r="K38" s="27" t="s">
+      <c r="K38" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="L38" s="4"/>
-      <c r="N38" s="6">
+      <c r="L38" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="N38" s="5">
         <v>35</v>
       </c>
-      <c r="O38" s="28">
+      <c r="O38" s="27">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="P38" s="6">
+      <c r="P38" s="5">
         <f t="shared" si="1"/>
         <v>201</v>
       </c>
-      <c r="Q38" s="6">
+      <c r="Q38" s="5">
         <v>8</v>
       </c>
-      <c r="R38" s="6">
+      <c r="R38" s="5">
         <f t="shared" si="3"/>
         <v>185</v>
       </c>
-      <c r="S38" s="15">
+      <c r="S38" s="14">
         <f t="shared" si="2"/>
         <v>46098</v>
       </c>
     </row>
     <row r="39" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E39" s="30" t="s">
+      <c r="E39" s="29" t="s">
         <v>94</v>
       </c>
-      <c r="F39" s="32" t="s">
+      <c r="F39" s="41" t="s">
         <v>99</v>
       </c>
-      <c r="G39" s="33" t="s">
+      <c r="G39" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="H39" s="34" t="s">
+      <c r="H39" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="I39" s="34">
+      <c r="I39" s="32">
         <v>8</v>
       </c>
-      <c r="J39" s="35">
+      <c r="J39" s="33">
         <v>2</v>
       </c>
-      <c r="K39" s="36" t="s">
+      <c r="K39" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="L39" s="37"/>
-      <c r="N39" s="6">
+      <c r="L39" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="N39" s="5">
         <v>36</v>
       </c>
-      <c r="O39" s="28">
+      <c r="O39" s="27">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="P39" s="6">
+      <c r="P39" s="5">
         <f t="shared" si="1"/>
         <v>198</v>
       </c>
-      <c r="Q39" s="6">
-        <v>0</v>
-      </c>
-      <c r="R39" s="6">
+      <c r="Q39" s="5">
+        <v>0</v>
+      </c>
+      <c r="R39" s="5">
         <f t="shared" si="3"/>
         <v>185</v>
       </c>
-      <c r="S39" s="15">
+      <c r="S39" s="14">
         <f t="shared" si="2"/>
         <v>46099</v>
       </c>
     </row>
     <row r="40" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E40" s="31" t="s">
+      <c r="E40" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="F40" s="38" t="s">
+      <c r="F40" s="42" t="s">
         <v>117</v>
       </c>
-      <c r="G40" s="39" t="s">
+      <c r="G40" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="H40" s="40" t="s">
+      <c r="H40" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="I40" s="40">
+      <c r="I40" s="37">
         <v>21</v>
       </c>
-      <c r="J40" s="12">
+      <c r="J40" s="11">
         <v>1</v>
       </c>
-      <c r="K40" s="13" t="s">
+      <c r="K40" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="L40" s="38"/>
-      <c r="N40" s="6">
+      <c r="L40" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="N40" s="5">
         <v>37</v>
       </c>
-      <c r="O40" s="28">
+      <c r="O40" s="27">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="P40" s="6">
+      <c r="P40" s="5">
         <f t="shared" si="1"/>
         <v>195</v>
       </c>
-      <c r="Q40" s="6">
+      <c r="Q40" s="5">
         <v>6</v>
       </c>
-      <c r="R40" s="6">
+      <c r="R40" s="5">
         <f t="shared" si="3"/>
         <v>179</v>
       </c>
-      <c r="S40" s="15">
+      <c r="S40" s="14">
         <f t="shared" si="2"/>
         <v>46100</v>
       </c>
     </row>
     <row r="41" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E41" s="31" t="s">
+      <c r="E41" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="F41" s="38" t="s">
+      <c r="F41" s="42" t="s">
         <v>119</v>
       </c>
-      <c r="G41" s="39" t="s">
+      <c r="G41" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="H41" s="41" t="s">
+      <c r="H41" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="I41" s="41">
+      <c r="I41" s="38">
         <v>13</v>
       </c>
-      <c r="J41" s="42">
+      <c r="J41" s="39">
         <v>2</v>
       </c>
-      <c r="K41" s="13" t="s">
+      <c r="K41" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="L41" s="38"/>
-      <c r="N41" s="6">
+      <c r="L41" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N41" s="5">
         <v>38</v>
       </c>
-      <c r="O41" s="28">
+      <c r="O41" s="27">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="P41" s="6">
+      <c r="P41" s="5">
         <f t="shared" si="1"/>
         <v>192</v>
       </c>
-      <c r="Q41" s="6">
-        <v>0</v>
-      </c>
-      <c r="R41" s="6">
+      <c r="Q41" s="5">
+        <v>0</v>
+      </c>
+      <c r="R41" s="5">
         <f t="shared" si="3"/>
         <v>179</v>
       </c>
-      <c r="S41" s="15">
+      <c r="S41" s="14">
         <f t="shared" si="2"/>
         <v>46101</v>
       </c>
     </row>
     <row r="42" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="N42" s="6">
+      <c r="N42" s="5">
         <v>39</v>
       </c>
-      <c r="O42" s="28">
+      <c r="O42" s="27">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="P42" s="6">
+      <c r="P42" s="5">
         <f t="shared" si="1"/>
         <v>189</v>
       </c>
-      <c r="Q42" s="6">
+      <c r="Q42" s="5">
         <v>8</v>
       </c>
-      <c r="R42" s="6">
+      <c r="R42" s="5">
         <f t="shared" si="3"/>
         <v>171</v>
       </c>
-      <c r="S42" s="15">
+      <c r="S42" s="14">
         <f t="shared" si="2"/>
         <v>46102</v>
       </c>
     </row>
     <row r="43" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="N43" s="6">
+      <c r="N43" s="5">
         <v>40</v>
       </c>
-      <c r="O43" s="28">
+      <c r="O43" s="27">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="P43" s="6">
+      <c r="P43" s="5">
         <f t="shared" si="1"/>
         <v>186</v>
       </c>
-      <c r="Q43" s="6">
+      <c r="Q43" s="5">
         <v>8</v>
       </c>
-      <c r="R43" s="6">
+      <c r="R43" s="5">
         <f t="shared" si="3"/>
         <v>163</v>
       </c>
-      <c r="S43" s="15">
+      <c r="S43" s="14">
         <f t="shared" si="2"/>
         <v>46103</v>
       </c>
     </row>
     <row r="44" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="N44" s="6">
+      <c r="N44" s="5">
         <v>41</v>
       </c>
-      <c r="O44" s="28">
+      <c r="O44" s="27">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="P44" s="6">
+      <c r="P44" s="5">
         <f t="shared" si="1"/>
         <v>183</v>
       </c>
-      <c r="Q44" s="6">
-        <v>0</v>
-      </c>
-      <c r="R44" s="6">
+      <c r="Q44" s="5">
+        <v>0</v>
+      </c>
+      <c r="R44" s="5">
         <f t="shared" si="3"/>
         <v>163</v>
       </c>
-      <c r="S44" s="15">
+      <c r="S44" s="14">
         <f t="shared" si="2"/>
         <v>46104</v>
       </c>
     </row>
     <row r="45" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="N45" s="6">
+      <c r="N45" s="5">
         <v>42</v>
       </c>
-      <c r="O45" s="28">
+      <c r="O45" s="27">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="P45" s="6">
+      <c r="P45" s="5">
         <f t="shared" si="1"/>
         <v>180</v>
       </c>
-      <c r="Q45" s="6">
+      <c r="Q45" s="5">
         <v>8</v>
       </c>
-      <c r="R45" s="6">
+      <c r="R45" s="5">
         <f t="shared" si="3"/>
         <v>155</v>
       </c>
-      <c r="S45" s="15">
+      <c r="S45" s="14">
         <f t="shared" si="2"/>
         <v>46105</v>
       </c>
     </row>
     <row r="46" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="N46" s="6">
+      <c r="N46" s="5">
         <v>43</v>
       </c>
-      <c r="O46" s="28">
+      <c r="O46" s="27">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="P46" s="6">
+      <c r="P46" s="5">
         <f t="shared" si="1"/>
         <v>177</v>
       </c>
-      <c r="Q46" s="6">
+      <c r="Q46" s="5">
         <v>10</v>
       </c>
-      <c r="R46" s="6">
+      <c r="R46" s="5">
         <f t="shared" si="3"/>
         <v>145</v>
       </c>
-      <c r="S46" s="15">
+      <c r="S46" s="14">
         <f t="shared" si="2"/>
         <v>46106</v>
       </c>
     </row>
     <row r="47" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="N47" s="6">
+      <c r="N47" s="5">
         <v>44</v>
       </c>
-      <c r="O47" s="28">
+      <c r="O47" s="27">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="P47" s="6">
+      <c r="P47" s="5">
         <f t="shared" si="1"/>
         <v>174</v>
       </c>
-      <c r="Q47" s="6">
-        <v>0</v>
-      </c>
-      <c r="R47" s="6">
+      <c r="Q47" s="5">
+        <v>0</v>
+      </c>
+      <c r="R47" s="5">
         <f t="shared" si="3"/>
         <v>145</v>
       </c>
-      <c r="S47" s="15">
+      <c r="S47" s="14">
         <f t="shared" si="2"/>
         <v>46107</v>
       </c>
     </row>
     <row r="48" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="N48" s="6">
+      <c r="N48" s="5">
         <v>45</v>
       </c>
-      <c r="O48" s="28">
+      <c r="O48" s="27">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="P48" s="6">
+      <c r="P48" s="5">
         <f t="shared" si="1"/>
         <v>171</v>
       </c>
-      <c r="Q48" s="6">
-        <v>0</v>
-      </c>
-      <c r="R48" s="6">
+      <c r="Q48" s="5">
+        <v>0</v>
+      </c>
+      <c r="R48" s="5">
         <f t="shared" si="3"/>
         <v>145</v>
       </c>
-      <c r="S48" s="15">
+      <c r="S48" s="14">
         <f t="shared" si="2"/>
         <v>46108</v>
       </c>
     </row>
     <row r="49" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N49" s="6">
+      <c r="N49" s="5">
         <v>46</v>
       </c>
-      <c r="O49" s="28">
+      <c r="O49" s="27">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="P49" s="6">
+      <c r="P49" s="5">
         <f t="shared" si="1"/>
         <v>168</v>
       </c>
-      <c r="Q49" s="6">
-        <v>0</v>
-      </c>
-      <c r="R49" s="6">
+      <c r="Q49" s="5">
+        <v>0</v>
+      </c>
+      <c r="R49" s="5">
         <f t="shared" si="3"/>
         <v>145</v>
       </c>
-      <c r="S49" s="15">
+      <c r="S49" s="14">
         <f t="shared" si="2"/>
         <v>46109</v>
       </c>
     </row>
     <row r="50" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N50" s="6">
+      <c r="N50" s="5">
         <v>47</v>
       </c>
-      <c r="O50" s="28">
+      <c r="O50" s="27">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="P50" s="6">
+      <c r="P50" s="5">
         <f t="shared" si="1"/>
         <v>165</v>
       </c>
-      <c r="Q50" s="6">
-        <v>0</v>
-      </c>
-      <c r="R50" s="6">
+      <c r="Q50" s="5">
+        <v>0</v>
+      </c>
+      <c r="R50" s="5">
         <f t="shared" si="3"/>
         <v>145</v>
       </c>
-      <c r="S50" s="15">
+      <c r="S50" s="14">
         <f t="shared" si="2"/>
         <v>46110</v>
       </c>
     </row>
     <row r="51" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N51" s="6">
+      <c r="N51" s="5">
         <v>48</v>
       </c>
-      <c r="O51" s="28">
+      <c r="O51" s="27">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="P51" s="6">
+      <c r="P51" s="5">
         <f t="shared" si="1"/>
         <v>162</v>
       </c>
-      <c r="Q51" s="6">
-        <v>0</v>
-      </c>
-      <c r="R51" s="6">
+      <c r="Q51" s="5">
+        <v>0</v>
+      </c>
+      <c r="R51" s="5">
         <f t="shared" si="3"/>
         <v>145</v>
       </c>
-      <c r="S51" s="15">
+      <c r="S51" s="14">
         <f t="shared" si="2"/>
         <v>46111</v>
       </c>
     </row>
     <row r="52" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N52" s="6">
+      <c r="N52" s="5">
         <v>49</v>
       </c>
-      <c r="O52" s="28">
+      <c r="O52" s="27">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="P52" s="6">
+      <c r="P52" s="5">
         <f t="shared" si="1"/>
         <v>159</v>
       </c>
-      <c r="Q52" s="6">
-        <v>0</v>
-      </c>
-      <c r="R52" s="6">
+      <c r="Q52" s="5">
+        <v>0</v>
+      </c>
+      <c r="R52" s="5">
         <f t="shared" si="3"/>
         <v>145</v>
       </c>
-      <c r="S52" s="15">
+      <c r="S52" s="14">
         <f t="shared" si="2"/>
         <v>46112</v>
       </c>
     </row>
     <row r="53" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N53" s="6">
+      <c r="N53" s="5">
         <v>50</v>
       </c>
-      <c r="O53" s="28">
+      <c r="O53" s="27">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="P53" s="6">
+      <c r="P53" s="5">
         <f t="shared" si="1"/>
         <v>156</v>
       </c>
-      <c r="Q53" s="6">
-        <v>0</v>
-      </c>
-      <c r="R53" s="6">
+      <c r="Q53" s="5">
+        <v>0</v>
+      </c>
+      <c r="R53" s="5">
         <f t="shared" si="3"/>
         <v>145</v>
       </c>
-      <c r="S53" s="15">
+      <c r="S53" s="14">
         <f t="shared" si="2"/>
         <v>46113</v>
       </c>
     </row>
     <row r="54" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N54" s="6">
+      <c r="N54" s="5">
         <v>51</v>
       </c>
-      <c r="O54" s="28">
+      <c r="O54" s="27">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="P54" s="6">
+      <c r="P54" s="5">
         <f t="shared" si="1"/>
         <v>153</v>
       </c>
-      <c r="Q54" s="6">
+      <c r="Q54" s="5">
         <v>8</v>
       </c>
-      <c r="R54" s="6">
+      <c r="R54" s="5">
         <f t="shared" si="3"/>
         <v>137</v>
       </c>
-      <c r="S54" s="15">
+      <c r="S54" s="14">
         <f t="shared" si="2"/>
         <v>46114</v>
       </c>
     </row>
     <row r="55" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N55" s="6">
+      <c r="N55" s="5">
         <v>52</v>
       </c>
-      <c r="O55" s="28">
+      <c r="O55" s="27">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="P55" s="6">
+      <c r="P55" s="5">
         <f t="shared" si="1"/>
         <v>150</v>
       </c>
-      <c r="Q55" s="6">
-        <v>0</v>
-      </c>
-      <c r="R55" s="6">
+      <c r="Q55" s="5">
+        <v>0</v>
+      </c>
+      <c r="R55" s="5">
         <f t="shared" si="3"/>
         <v>137</v>
       </c>
-      <c r="S55" s="15">
+      <c r="S55" s="14">
         <f t="shared" si="2"/>
         <v>46115</v>
       </c>
     </row>
     <row r="56" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N56" s="6">
+      <c r="N56" s="5">
         <v>53</v>
       </c>
-      <c r="O56" s="28">
+      <c r="O56" s="27">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="P56" s="6">
+      <c r="P56" s="5">
         <f t="shared" si="1"/>
         <v>147</v>
       </c>
-      <c r="Q56" s="6">
-        <v>0</v>
-      </c>
-      <c r="R56" s="6">
+      <c r="Q56" s="5">
+        <v>0</v>
+      </c>
+      <c r="R56" s="5">
         <f t="shared" si="3"/>
         <v>137</v>
       </c>
-      <c r="S56" s="15">
+      <c r="S56" s="14">
         <f t="shared" si="2"/>
         <v>46116</v>
       </c>
     </row>
     <row r="57" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N57" s="6">
+      <c r="N57" s="5">
         <v>54</v>
       </c>
-      <c r="O57" s="28">
+      <c r="O57" s="27">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="P57" s="6">
+      <c r="P57" s="5">
         <f t="shared" si="1"/>
         <v>144</v>
       </c>
-      <c r="Q57" s="6">
-        <v>0</v>
-      </c>
-      <c r="R57" s="6">
+      <c r="Q57" s="5">
+        <v>0</v>
+      </c>
+      <c r="R57" s="5">
         <f t="shared" si="3"/>
         <v>137</v>
       </c>
-      <c r="S57" s="15">
+      <c r="S57" s="14">
         <f t="shared" si="2"/>
         <v>46117</v>
       </c>
     </row>
     <row r="58" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N58" s="6">
+      <c r="N58" s="5">
         <v>55</v>
       </c>
-      <c r="O58" s="28">
+      <c r="O58" s="27">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="P58" s="6">
+      <c r="P58" s="5">
         <f t="shared" si="1"/>
         <v>141</v>
       </c>
-      <c r="Q58" s="6">
+      <c r="Q58" s="5">
         <v>13</v>
       </c>
-      <c r="R58" s="6">
+      <c r="R58" s="5">
         <f t="shared" si="3"/>
         <v>124</v>
       </c>
-      <c r="S58" s="15">
+      <c r="S58" s="14">
         <f t="shared" si="2"/>
         <v>46118</v>
       </c>
     </row>
     <row r="59" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N59" s="6">
+      <c r="N59" s="5">
         <v>56</v>
       </c>
-      <c r="O59" s="28">
+      <c r="O59" s="27">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="P59" s="6">
+      <c r="P59" s="5">
         <f t="shared" si="1"/>
         <v>138</v>
       </c>
-      <c r="Q59" s="6">
-        <v>0</v>
-      </c>
-      <c r="R59" s="6">
+      <c r="Q59" s="5">
+        <v>0</v>
+      </c>
+      <c r="R59" s="5">
         <f t="shared" si="3"/>
         <v>124</v>
       </c>
-      <c r="S59" s="15">
+      <c r="S59" s="14">
         <f t="shared" si="2"/>
         <v>46119</v>
       </c>
     </row>
     <row r="60" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N60" s="6">
+      <c r="N60" s="5">
         <v>57</v>
       </c>
-      <c r="O60" s="28">
+      <c r="O60" s="27">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="P60" s="6">
+      <c r="P60" s="5">
         <f t="shared" si="1"/>
         <v>135</v>
       </c>
-      <c r="Q60" s="6">
-        <v>3</v>
-      </c>
-      <c r="R60" s="6">
+      <c r="Q60" s="5">
+        <v>3</v>
+      </c>
+      <c r="R60" s="5">
         <f t="shared" si="3"/>
         <v>121</v>
       </c>
-      <c r="S60" s="15">
+      <c r="S60" s="14">
         <f t="shared" si="2"/>
         <v>46120</v>
       </c>
     </row>
     <row r="61" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N61" s="6">
+      <c r="N61" s="5">
         <v>58</v>
       </c>
-      <c r="O61" s="28">
+      <c r="O61" s="27">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="P61" s="6">
+      <c r="P61" s="5">
         <f t="shared" si="1"/>
         <v>132</v>
       </c>
-      <c r="Q61" s="6">
-        <v>0</v>
-      </c>
-      <c r="R61" s="6">
+      <c r="Q61" s="5">
+        <v>0</v>
+      </c>
+      <c r="R61" s="5">
         <f t="shared" si="3"/>
         <v>121</v>
       </c>
-      <c r="S61" s="15">
+      <c r="S61" s="14">
         <f t="shared" si="2"/>
         <v>46121</v>
       </c>
     </row>
     <row r="62" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N62" s="6">
+      <c r="N62" s="5">
         <v>59</v>
       </c>
-      <c r="O62" s="28">
+      <c r="O62" s="27">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="P62" s="6">
+      <c r="P62" s="5">
         <f t="shared" si="1"/>
         <v>129</v>
       </c>
-      <c r="Q62" s="6">
-        <v>0</v>
-      </c>
-      <c r="R62" s="6">
+      <c r="Q62" s="5">
+        <v>0</v>
+      </c>
+      <c r="R62" s="5">
         <f t="shared" si="3"/>
         <v>121</v>
       </c>
-      <c r="S62" s="15">
+      <c r="S62" s="14">
         <f t="shared" si="2"/>
         <v>46122</v>
       </c>
     </row>
     <row r="63" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N63" s="6">
+      <c r="N63" s="5">
         <v>60</v>
       </c>
-      <c r="O63" s="28">
+      <c r="O63" s="27">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="P63" s="6">
+      <c r="P63" s="5">
         <f t="shared" si="1"/>
         <v>126</v>
       </c>
-      <c r="Q63" s="6">
-        <v>0</v>
-      </c>
-      <c r="R63" s="6">
+      <c r="Q63" s="5">
+        <v>0</v>
+      </c>
+      <c r="R63" s="5">
         <f t="shared" si="3"/>
         <v>121</v>
       </c>
-      <c r="S63" s="15">
+      <c r="S63" s="14">
         <f t="shared" si="2"/>
         <v>46123</v>
       </c>
     </row>
     <row r="64" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N64" s="6">
+      <c r="N64" s="5">
         <v>61</v>
       </c>
-      <c r="O64" s="28">
+      <c r="O64" s="27">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="P64" s="6">
+      <c r="P64" s="5">
         <f t="shared" si="1"/>
         <v>123</v>
       </c>
-      <c r="Q64" s="6">
+      <c r="Q64" s="5">
         <v>8</v>
       </c>
-      <c r="R64" s="6">
+      <c r="R64" s="5">
         <f t="shared" si="3"/>
         <v>113</v>
       </c>
-      <c r="S64" s="15">
+      <c r="S64" s="14">
         <f t="shared" si="2"/>
         <v>46124</v>
       </c>
     </row>
     <row r="65" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N65" s="6">
+      <c r="N65" s="5">
         <v>62</v>
       </c>
-      <c r="O65" s="28">
+      <c r="O65" s="27">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="P65" s="6">
+      <c r="P65" s="5">
         <f t="shared" si="1"/>
         <v>120</v>
       </c>
-      <c r="Q65" s="6">
-        <v>0</v>
-      </c>
-      <c r="R65" s="6">
+      <c r="Q65" s="5">
+        <v>0</v>
+      </c>
+      <c r="R65" s="5">
         <f t="shared" si="3"/>
         <v>113</v>
       </c>
-      <c r="S65" s="15">
+      <c r="S65" s="14">
         <f t="shared" si="2"/>
         <v>46125</v>
       </c>
     </row>
     <row r="66" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N66" s="6">
+      <c r="N66" s="5">
         <v>63</v>
       </c>
-      <c r="O66" s="28">
+      <c r="O66" s="27">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="P66" s="6">
+      <c r="P66" s="5">
         <f t="shared" si="1"/>
         <v>117</v>
       </c>
-      <c r="Q66" s="6">
-        <v>0</v>
-      </c>
-      <c r="R66" s="6">
+      <c r="Q66" s="5">
+        <v>0</v>
+      </c>
+      <c r="R66" s="5">
         <f t="shared" si="3"/>
         <v>113</v>
       </c>
-      <c r="S66" s="15">
+      <c r="S66" s="14">
         <f t="shared" si="2"/>
         <v>46126</v>
       </c>
     </row>
     <row r="67" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N67" s="6">
+      <c r="N67" s="5">
         <v>64</v>
       </c>
-      <c r="O67" s="28">
+      <c r="O67" s="27">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="P67" s="6">
+      <c r="P67" s="5">
         <f t="shared" si="1"/>
         <v>114</v>
       </c>
-      <c r="Q67" s="6">
-        <v>0</v>
-      </c>
-      <c r="R67" s="6">
+      <c r="Q67" s="5">
+        <v>0</v>
+      </c>
+      <c r="R67" s="5">
         <f t="shared" si="3"/>
         <v>113</v>
       </c>
-      <c r="S67" s="15">
+      <c r="S67" s="14">
         <f t="shared" si="2"/>
         <v>46127</v>
       </c>
     </row>
     <row r="68" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N68" s="6">
+      <c r="N68" s="5">
         <v>65</v>
       </c>
-      <c r="O68" s="28">
+      <c r="O68" s="27">
         <f t="shared" ref="O68:O99" si="5">$B$10</f>
         <v>3</v>
       </c>
-      <c r="P68" s="6">
+      <c r="P68" s="5">
         <f t="shared" si="1"/>
         <v>111</v>
       </c>
-      <c r="Q68" s="6">
-        <v>0</v>
-      </c>
-      <c r="R68" s="6">
+      <c r="Q68" s="5">
+        <v>0</v>
+      </c>
+      <c r="R68" s="5">
         <f t="shared" si="3"/>
         <v>113</v>
       </c>
-      <c r="S68" s="15">
+      <c r="S68" s="14">
         <f t="shared" si="2"/>
         <v>46128</v>
       </c>
     </row>
     <row r="69" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N69" s="6">
+      <c r="N69" s="5">
         <v>66</v>
       </c>
-      <c r="O69" s="28">
+      <c r="O69" s="27">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="P69" s="6">
+      <c r="P69" s="5">
         <f t="shared" ref="P69:P93" si="6">P68-$O$4</f>
         <v>108</v>
       </c>
-      <c r="Q69" s="6">
-        <v>0</v>
-      </c>
-      <c r="R69" s="6">
+      <c r="Q69" s="5">
+        <v>0</v>
+      </c>
+      <c r="R69" s="5">
         <f t="shared" si="3"/>
         <v>113</v>
       </c>
-      <c r="S69" s="15">
-        <f t="shared" ref="S69:S117" si="7">S68+1</f>
+      <c r="S69" s="14">
+        <f t="shared" ref="S69:S122" si="7">S68+1</f>
         <v>46129</v>
       </c>
     </row>
     <row r="70" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N70" s="6">
+      <c r="N70" s="5">
         <v>67</v>
       </c>
-      <c r="O70" s="28">
+      <c r="O70" s="27">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="P70" s="6">
+      <c r="P70" s="5">
         <f t="shared" si="6"/>
         <v>105</v>
       </c>
-      <c r="Q70" s="6">
-        <v>0</v>
-      </c>
-      <c r="R70" s="6">
+      <c r="Q70" s="5">
+        <v>0</v>
+      </c>
+      <c r="R70" s="5">
         <f t="shared" ref="R70:R117" si="8">IF(Q70&lt;&gt;"",R69-Q70,R69)</f>
         <v>113</v>
       </c>
-      <c r="S70" s="15">
+      <c r="S70" s="14">
         <f t="shared" si="7"/>
         <v>46130</v>
       </c>
     </row>
     <row r="71" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N71" s="6">
+      <c r="N71" s="5">
         <v>68</v>
       </c>
-      <c r="O71" s="28">
+      <c r="O71" s="27">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="P71" s="6">
+      <c r="P71" s="5">
         <f t="shared" si="6"/>
         <v>102</v>
       </c>
-      <c r="Q71" s="6">
-        <v>0</v>
-      </c>
-      <c r="R71" s="6">
+      <c r="Q71" s="5">
+        <v>0</v>
+      </c>
+      <c r="R71" s="5">
         <f t="shared" si="8"/>
         <v>113</v>
       </c>
-      <c r="S71" s="15">
+      <c r="S71" s="14">
         <f t="shared" si="7"/>
         <v>46131</v>
       </c>
     </row>
     <row r="72" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N72" s="6">
+      <c r="N72" s="5">
         <v>69</v>
       </c>
-      <c r="O72" s="28">
+      <c r="O72" s="27">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="P72" s="6">
+      <c r="P72" s="5">
         <f t="shared" si="6"/>
         <v>99</v>
       </c>
-      <c r="Q72" s="6">
-        <v>0</v>
-      </c>
-      <c r="R72" s="6">
+      <c r="Q72" s="5">
+        <v>0</v>
+      </c>
+      <c r="R72" s="5">
         <f t="shared" si="8"/>
         <v>113</v>
       </c>
-      <c r="S72" s="15">
+      <c r="S72" s="14">
         <f t="shared" si="7"/>
         <v>46132</v>
       </c>
     </row>
     <row r="73" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N73" s="6">
+      <c r="N73" s="5">
         <v>70</v>
       </c>
-      <c r="O73" s="28">
+      <c r="O73" s="27">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="P73" s="6">
+      <c r="P73" s="5">
         <f t="shared" si="6"/>
         <v>96</v>
       </c>
-      <c r="Q73" s="6">
-        <v>0</v>
-      </c>
-      <c r="R73" s="6">
+      <c r="Q73" s="5">
+        <v>0</v>
+      </c>
+      <c r="R73" s="5">
         <f t="shared" si="8"/>
         <v>113</v>
       </c>
-      <c r="S73" s="15">
+      <c r="S73" s="14">
         <f t="shared" si="7"/>
         <v>46133</v>
       </c>
     </row>
     <row r="74" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N74" s="6">
+      <c r="N74" s="5">
         <v>71</v>
       </c>
-      <c r="O74" s="28">
+      <c r="O74" s="27">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="P74" s="6">
+      <c r="P74" s="5">
         <f t="shared" si="6"/>
         <v>93</v>
       </c>
-      <c r="Q74" s="6">
-        <v>3</v>
-      </c>
-      <c r="R74" s="6">
+      <c r="Q74" s="5">
+        <v>3</v>
+      </c>
+      <c r="R74" s="5">
         <f t="shared" si="8"/>
         <v>110</v>
       </c>
-      <c r="S74" s="15">
+      <c r="S74" s="14">
         <f t="shared" si="7"/>
         <v>46134</v>
       </c>
     </row>
     <row r="75" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N75" s="6">
+      <c r="N75" s="5">
         <v>72</v>
       </c>
-      <c r="O75" s="28">
+      <c r="O75" s="27">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="P75" s="6">
+      <c r="P75" s="5">
         <f t="shared" si="6"/>
         <v>90</v>
       </c>
-      <c r="Q75" s="6">
-        <v>0</v>
-      </c>
-      <c r="R75" s="6">
+      <c r="Q75" s="5">
+        <v>0</v>
+      </c>
+      <c r="R75" s="5">
         <f t="shared" si="8"/>
         <v>110</v>
       </c>
-      <c r="S75" s="15">
+      <c r="S75" s="14">
         <f t="shared" si="7"/>
         <v>46135</v>
       </c>
     </row>
     <row r="76" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N76" s="6">
+      <c r="N76" s="5">
         <v>73</v>
       </c>
-      <c r="O76" s="28">
+      <c r="O76" s="27">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="P76" s="6">
+      <c r="P76" s="5">
         <f t="shared" si="6"/>
         <v>87</v>
       </c>
-      <c r="Q76" s="6">
+      <c r="Q76" s="5">
         <v>13</v>
       </c>
-      <c r="R76" s="6">
+      <c r="R76" s="5">
         <f t="shared" si="8"/>
         <v>97</v>
       </c>
-      <c r="S76" s="15">
+      <c r="S76" s="14">
         <f t="shared" si="7"/>
         <v>46136</v>
       </c>
     </row>
     <row r="77" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N77" s="6">
+      <c r="N77" s="5">
         <v>74</v>
       </c>
-      <c r="O77" s="28">
+      <c r="O77" s="27">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="P77" s="6">
+      <c r="P77" s="5">
         <f t="shared" si="6"/>
         <v>84</v>
       </c>
-      <c r="Q77" s="6">
-        <v>0</v>
-      </c>
-      <c r="R77" s="6">
+      <c r="Q77" s="5">
+        <v>0</v>
+      </c>
+      <c r="R77" s="5">
         <f t="shared" si="8"/>
         <v>97</v>
       </c>
-      <c r="S77" s="15">
+      <c r="S77" s="14">
         <f t="shared" si="7"/>
         <v>46137</v>
       </c>
     </row>
     <row r="78" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N78" s="6">
+      <c r="N78" s="5">
         <v>75</v>
       </c>
-      <c r="O78" s="28">
+      <c r="O78" s="27">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="P78" s="6">
+      <c r="P78" s="5">
         <f t="shared" si="6"/>
         <v>81</v>
       </c>
-      <c r="Q78" s="6">
-        <v>0</v>
-      </c>
-      <c r="R78" s="6">
+      <c r="Q78" s="5">
+        <v>0</v>
+      </c>
+      <c r="R78" s="5">
         <f t="shared" si="8"/>
         <v>97</v>
       </c>
-      <c r="S78" s="15">
+      <c r="S78" s="14">
         <f t="shared" si="7"/>
         <v>46138</v>
       </c>
     </row>
     <row r="79" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N79" s="6">
+      <c r="N79" s="5">
         <v>76</v>
       </c>
-      <c r="O79" s="28">
+      <c r="O79" s="27">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="P79" s="6">
+      <c r="P79" s="5">
         <f t="shared" si="6"/>
         <v>78</v>
       </c>
-      <c r="Q79" s="6">
-        <v>0</v>
-      </c>
-      <c r="R79" s="6">
+      <c r="Q79" s="5">
+        <v>0</v>
+      </c>
+      <c r="R79" s="5">
         <f t="shared" si="8"/>
         <v>97</v>
       </c>
-      <c r="S79" s="15">
+      <c r="S79" s="14">
         <f t="shared" si="7"/>
         <v>46139</v>
       </c>
     </row>
     <row r="80" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N80" s="6">
+      <c r="N80" s="5">
         <v>77</v>
       </c>
-      <c r="O80" s="28">
+      <c r="O80" s="27">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="P80" s="6">
+      <c r="P80" s="5">
         <f t="shared" si="6"/>
         <v>75</v>
       </c>
-      <c r="Q80" s="6">
-        <v>0</v>
-      </c>
-      <c r="R80" s="6">
+      <c r="Q80" s="5">
+        <v>0</v>
+      </c>
+      <c r="R80" s="5">
         <f t="shared" si="8"/>
         <v>97</v>
       </c>
-      <c r="S80" s="15">
+      <c r="S80" s="14">
         <f t="shared" si="7"/>
         <v>46140</v>
       </c>
     </row>
     <row r="81" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N81" s="6">
+      <c r="N81" s="5">
         <v>78</v>
       </c>
-      <c r="O81" s="28">
+      <c r="O81" s="27">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="P81" s="6">
+      <c r="P81" s="5">
         <f t="shared" si="6"/>
         <v>72</v>
       </c>
-      <c r="Q81" s="6">
-        <v>0</v>
-      </c>
-      <c r="R81" s="6">
+      <c r="Q81" s="5">
+        <v>0</v>
+      </c>
+      <c r="R81" s="5">
         <f t="shared" si="8"/>
         <v>97</v>
       </c>
-      <c r="S81" s="15">
+      <c r="S81" s="14">
         <f t="shared" si="7"/>
         <v>46141</v>
       </c>
     </row>
     <row r="82" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N82" s="6">
+      <c r="N82" s="5">
         <v>79</v>
       </c>
-      <c r="O82" s="28">
+      <c r="O82" s="27">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="P82" s="6">
+      <c r="P82" s="5">
         <f t="shared" si="6"/>
         <v>69</v>
       </c>
-      <c r="Q82" s="6">
-        <v>0</v>
-      </c>
-      <c r="R82" s="6">
+      <c r="Q82" s="5">
+        <v>0</v>
+      </c>
+      <c r="R82" s="5">
         <f t="shared" si="8"/>
         <v>97</v>
       </c>
-      <c r="S82" s="15">
+      <c r="S82" s="14">
         <f t="shared" si="7"/>
         <v>46142</v>
       </c>
     </row>
     <row r="83" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N83" s="6">
+      <c r="N83" s="5">
         <v>80</v>
       </c>
-      <c r="O83" s="28">
+      <c r="O83" s="27">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="P83" s="6">
+      <c r="P83" s="5">
         <f t="shared" si="6"/>
         <v>66</v>
       </c>
-      <c r="Q83" s="6">
-        <v>0</v>
-      </c>
-      <c r="R83" s="6">
+      <c r="Q83" s="5">
+        <v>0</v>
+      </c>
+      <c r="R83" s="5">
         <f t="shared" si="8"/>
         <v>97</v>
       </c>
-      <c r="S83" s="15">
+      <c r="S83" s="14">
         <f t="shared" si="7"/>
         <v>46143</v>
       </c>
     </row>
     <row r="84" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N84" s="6">
+      <c r="N84" s="5">
         <v>81</v>
       </c>
-      <c r="O84" s="28">
+      <c r="O84" s="27">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="P84" s="6">
+      <c r="P84" s="5">
         <f t="shared" si="6"/>
         <v>63</v>
       </c>
-      <c r="Q84" s="6">
-        <v>0</v>
-      </c>
-      <c r="R84" s="6">
+      <c r="Q84" s="5">
+        <v>0</v>
+      </c>
+      <c r="R84" s="5">
         <f t="shared" si="8"/>
         <v>97</v>
       </c>
-      <c r="S84" s="15">
+      <c r="S84" s="14">
         <f t="shared" si="7"/>
         <v>46144</v>
       </c>
     </row>
     <row r="85" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N85" s="6">
+      <c r="N85" s="5">
         <v>82</v>
       </c>
-      <c r="O85" s="28">
+      <c r="O85" s="27">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="P85" s="6">
+      <c r="P85" s="5">
         <f t="shared" si="6"/>
         <v>60</v>
       </c>
-      <c r="Q85" s="6">
-        <v>0</v>
-      </c>
-      <c r="R85" s="6">
+      <c r="Q85" s="5">
+        <v>0</v>
+      </c>
+      <c r="R85" s="5">
         <f t="shared" si="8"/>
         <v>97</v>
       </c>
-      <c r="S85" s="15">
+      <c r="S85" s="14">
         <f t="shared" si="7"/>
         <v>46145</v>
       </c>
     </row>
     <row r="86" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N86" s="6">
+      <c r="N86" s="5">
         <v>83</v>
       </c>
-      <c r="O86" s="28">
+      <c r="O86" s="27">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="P86" s="6">
+      <c r="P86" s="5">
         <f t="shared" si="6"/>
         <v>57</v>
       </c>
-      <c r="Q86" s="6">
-        <v>0</v>
-      </c>
-      <c r="R86" s="6">
+      <c r="Q86" s="5">
+        <v>0</v>
+      </c>
+      <c r="R86" s="5">
         <f t="shared" si="8"/>
         <v>97</v>
       </c>
-      <c r="S86" s="15">
+      <c r="S86" s="14">
         <f t="shared" si="7"/>
         <v>46146</v>
       </c>
     </row>
     <row r="87" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N87" s="6">
+      <c r="N87" s="5">
         <v>84</v>
       </c>
-      <c r="O87" s="28">
+      <c r="O87" s="27">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="P87" s="6">
+      <c r="P87" s="5">
         <f t="shared" si="6"/>
         <v>54</v>
       </c>
-      <c r="Q87" s="6">
-        <v>0</v>
-      </c>
-      <c r="R87" s="6">
+      <c r="Q87" s="5">
+        <v>0</v>
+      </c>
+      <c r="R87" s="5">
         <f t="shared" si="8"/>
         <v>97</v>
       </c>
-      <c r="S87" s="15">
+      <c r="S87" s="14">
         <f t="shared" si="7"/>
         <v>46147</v>
       </c>
     </row>
     <row r="88" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N88" s="6">
+      <c r="N88" s="5">
         <v>85</v>
       </c>
-      <c r="O88" s="28">
+      <c r="O88" s="27">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="P88" s="6">
+      <c r="P88" s="5">
         <f t="shared" si="6"/>
         <v>51</v>
       </c>
-      <c r="Q88" s="6"/>
-      <c r="R88" s="6">
+      <c r="Q88" s="5">
+        <v>0</v>
+      </c>
+      <c r="R88" s="5">
         <f t="shared" si="8"/>
         <v>97</v>
       </c>
-      <c r="S88" s="16">
+      <c r="S88" s="15">
         <f t="shared" si="7"/>
         <v>46148</v>
       </c>
     </row>
     <row r="89" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N89" s="6">
+      <c r="N89" s="5">
         <v>86</v>
       </c>
-      <c r="O89" s="28">
+      <c r="O89" s="27">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="P89" s="6">
+      <c r="P89" s="5">
         <f t="shared" si="6"/>
         <v>48</v>
       </c>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="6">
+      <c r="Q89" s="5">
+        <v>0</v>
+      </c>
+      <c r="R89" s="5">
         <f t="shared" si="8"/>
         <v>97</v>
       </c>
-      <c r="S89" s="16">
+      <c r="S89" s="15">
         <f t="shared" si="7"/>
         <v>46149</v>
       </c>
     </row>
     <row r="90" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N90" s="6">
+      <c r="N90" s="5">
         <v>87</v>
       </c>
-      <c r="O90" s="28">
+      <c r="O90" s="27">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="P90" s="6">
+      <c r="P90" s="5">
         <f t="shared" si="6"/>
         <v>45</v>
       </c>
-      <c r="Q90" s="6"/>
-      <c r="R90" s="6">
+      <c r="Q90" s="5">
+        <v>0</v>
+      </c>
+      <c r="R90" s="5">
         <f t="shared" si="8"/>
         <v>97</v>
       </c>
-      <c r="S90" s="16">
+      <c r="S90" s="15">
         <f t="shared" si="7"/>
         <v>46150</v>
       </c>
     </row>
     <row r="91" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N91" s="6">
+      <c r="N91" s="5">
         <v>88</v>
       </c>
-      <c r="O91" s="28">
+      <c r="O91" s="27">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="P91" s="6">
+      <c r="P91" s="5">
         <f t="shared" si="6"/>
         <v>42</v>
       </c>
-      <c r="Q91" s="6"/>
-      <c r="R91" s="6">
+      <c r="Q91" s="5">
+        <v>0</v>
+      </c>
+      <c r="R91" s="5">
         <f t="shared" si="8"/>
         <v>97</v>
       </c>
-      <c r="S91" s="16">
+      <c r="S91" s="15">
         <f t="shared" si="7"/>
         <v>46151</v>
       </c>
     </row>
     <row r="92" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N92" s="6">
+      <c r="N92" s="5">
         <v>89</v>
       </c>
-      <c r="O92" s="28">
+      <c r="O92" s="27">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="P92" s="6">
+      <c r="P92" s="5">
         <f t="shared" si="6"/>
         <v>39</v>
       </c>
-      <c r="Q92" s="6"/>
-      <c r="R92" s="6">
+      <c r="Q92" s="5">
+        <v>0</v>
+      </c>
+      <c r="R92" s="5">
         <f t="shared" si="8"/>
         <v>97</v>
       </c>
-      <c r="S92" s="16">
+      <c r="S92" s="15">
         <f t="shared" si="7"/>
         <v>46152</v>
       </c>
     </row>
     <row r="93" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N93" s="6">
+      <c r="N93" s="5">
         <v>90</v>
       </c>
-      <c r="O93" s="28">
+      <c r="O93" s="27">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="P93" s="6">
+      <c r="P93" s="5">
         <f t="shared" si="6"/>
         <v>36</v>
       </c>
-      <c r="Q93" s="6"/>
-      <c r="R93" s="6">
+      <c r="Q93" s="5">
+        <v>0</v>
+      </c>
+      <c r="R93" s="5">
         <f t="shared" si="8"/>
         <v>97</v>
       </c>
-      <c r="S93" s="16">
+      <c r="S93" s="15">
         <f t="shared" si="7"/>
         <v>46153</v>
       </c>
     </row>
     <row r="94" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N94" s="6">
+      <c r="N94" s="5">
         <v>91</v>
       </c>
-      <c r="O94" s="28">
+      <c r="O94" s="27">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="P94" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="6"/>
-      <c r="R94" s="6">
+      <c r="P94" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="5">
+        <v>13</v>
+      </c>
+      <c r="R94" s="5">
         <f t="shared" si="8"/>
-        <v>97</v>
-      </c>
-      <c r="S94" s="16">
+        <v>84</v>
+      </c>
+      <c r="S94" s="15">
         <f t="shared" si="7"/>
         <v>46154</v>
       </c>
     </row>
     <row r="95" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N95" s="6">
+      <c r="N95" s="5">
         <v>92</v>
       </c>
-      <c r="O95" s="28">
+      <c r="O95" s="27">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="P95" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q95" s="6"/>
-      <c r="R95" s="6">
+      <c r="P95" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q95" s="5">
+        <v>21</v>
+      </c>
+      <c r="R95" s="5">
         <f t="shared" si="8"/>
-        <v>97</v>
-      </c>
-      <c r="S95" s="16">
+        <v>63</v>
+      </c>
+      <c r="S95" s="15">
         <f t="shared" si="7"/>
         <v>46155</v>
       </c>
     </row>
     <row r="96" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N96" s="6">
+      <c r="N96" s="5">
         <v>93</v>
       </c>
-      <c r="O96" s="28">
+      <c r="O96" s="27">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="P96" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="6"/>
-      <c r="R96" s="6">
+      <c r="P96" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="5">
+        <v>16</v>
+      </c>
+      <c r="R96" s="5">
         <f t="shared" si="8"/>
-        <v>97</v>
-      </c>
-      <c r="S96" s="16">
+        <v>47</v>
+      </c>
+      <c r="S96" s="15">
         <f t="shared" si="7"/>
         <v>46156</v>
       </c>
     </row>
     <row r="97" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N97" s="6">
+      <c r="N97" s="5">
         <v>94</v>
       </c>
-      <c r="O97" s="28">
+      <c r="O97" s="27">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="P97" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q97" s="6"/>
-      <c r="R97" s="6">
+      <c r="P97" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="5">
+        <v>0</v>
+      </c>
+      <c r="R97" s="5">
         <f t="shared" si="8"/>
-        <v>97</v>
-      </c>
-      <c r="S97" s="16">
+        <v>47</v>
+      </c>
+      <c r="S97" s="15">
         <f t="shared" si="7"/>
         <v>46157</v>
       </c>
     </row>
     <row r="98" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N98" s="6">
+      <c r="N98" s="5">
         <v>95</v>
       </c>
-      <c r="O98" s="28">
+      <c r="O98" s="27">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="P98" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q98" s="6"/>
-      <c r="R98" s="6">
+      <c r="P98" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="5">
+        <v>0</v>
+      </c>
+      <c r="R98" s="5">
         <f t="shared" si="8"/>
-        <v>97</v>
-      </c>
-      <c r="S98" s="16">
+        <v>47</v>
+      </c>
+      <c r="S98" s="15">
         <f t="shared" si="7"/>
         <v>46158</v>
       </c>
     </row>
     <row r="99" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N99" s="6">
+      <c r="N99" s="5">
         <v>96</v>
       </c>
-      <c r="O99" s="28">
+      <c r="O99" s="27">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="P99" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q99" s="6"/>
-      <c r="R99" s="6">
+      <c r="P99" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="5">
+        <v>0</v>
+      </c>
+      <c r="R99" s="5">
         <f t="shared" si="8"/>
-        <v>97</v>
-      </c>
-      <c r="S99" s="16">
+        <v>47</v>
+      </c>
+      <c r="S99" s="15">
         <f t="shared" si="7"/>
         <v>46159</v>
       </c>
     </row>
     <row r="100" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N100" s="6">
+      <c r="N100" s="5">
         <v>97</v>
       </c>
-      <c r="O100" s="28">
-        <f t="shared" ref="O100:O117" si="9">$B$10</f>
-        <v>3</v>
-      </c>
-      <c r="P100" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="6"/>
-      <c r="R100" s="6">
+      <c r="O100" s="27">
+        <f t="shared" ref="O100:O122" si="9">$B$10</f>
+        <v>3</v>
+      </c>
+      <c r="P100" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="5">
+        <v>0</v>
+      </c>
+      <c r="R100" s="5">
         <f t="shared" si="8"/>
-        <v>97</v>
-      </c>
-      <c r="S100" s="16">
+        <v>47</v>
+      </c>
+      <c r="S100" s="15">
         <f t="shared" si="7"/>
         <v>46160</v>
       </c>
     </row>
     <row r="101" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N101" s="6">
+      <c r="N101" s="5">
         <v>98</v>
       </c>
-      <c r="O101" s="28">
+      <c r="O101" s="27">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="P101" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="6"/>
-      <c r="R101" s="6">
+      <c r="P101" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="5">
+        <v>0</v>
+      </c>
+      <c r="R101" s="5">
         <f t="shared" si="8"/>
-        <v>97</v>
-      </c>
-      <c r="S101" s="16">
+        <v>47</v>
+      </c>
+      <c r="S101" s="15">
         <f t="shared" si="7"/>
         <v>46161</v>
       </c>
     </row>
     <row r="102" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N102" s="6">
+      <c r="N102" s="5">
         <v>99</v>
       </c>
-      <c r="O102" s="28">
+      <c r="O102" s="27">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="P102" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q102" s="6"/>
-      <c r="R102" s="6">
+      <c r="P102" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="5">
+        <v>8</v>
+      </c>
+      <c r="R102" s="5">
         <f t="shared" si="8"/>
-        <v>97</v>
-      </c>
-      <c r="S102" s="16">
+        <v>39</v>
+      </c>
+      <c r="S102" s="15">
         <f t="shared" si="7"/>
         <v>46162</v>
       </c>
     </row>
     <row r="103" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N103" s="6">
+      <c r="N103" s="5">
         <v>100</v>
       </c>
-      <c r="O103" s="28">
+      <c r="O103" s="27">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="P103" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q103" s="6"/>
-      <c r="R103" s="6">
+      <c r="P103" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q103" s="5">
+        <v>0</v>
+      </c>
+      <c r="R103" s="5">
         <f t="shared" si="8"/>
-        <v>97</v>
-      </c>
-      <c r="S103" s="16">
+        <v>39</v>
+      </c>
+      <c r="S103" s="15">
         <f t="shared" si="7"/>
         <v>46163</v>
       </c>
     </row>
     <row r="104" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N104" s="6">
+      <c r="N104" s="5">
         <v>101</v>
       </c>
-      <c r="O104" s="28">
+      <c r="O104" s="27">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="P104" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q104" s="6"/>
-      <c r="R104" s="6">
+      <c r="P104" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q104" s="5">
+        <v>0</v>
+      </c>
+      <c r="R104" s="5">
         <f t="shared" si="8"/>
-        <v>97</v>
-      </c>
-      <c r="S104" s="16">
+        <v>39</v>
+      </c>
+      <c r="S104" s="15">
         <f t="shared" si="7"/>
         <v>46164</v>
       </c>
     </row>
     <row r="105" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N105" s="6">
+      <c r="N105" s="5">
         <v>102</v>
       </c>
-      <c r="O105" s="28">
+      <c r="O105" s="27">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="P105" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q105" s="6"/>
-      <c r="R105" s="6">
+      <c r="P105" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q105" s="5">
+        <v>0</v>
+      </c>
+      <c r="R105" s="5">
         <f t="shared" si="8"/>
-        <v>97</v>
-      </c>
-      <c r="S105" s="16">
+        <v>39</v>
+      </c>
+      <c r="S105" s="15">
         <f t="shared" si="7"/>
         <v>46165</v>
       </c>
     </row>
     <row r="106" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N106" s="6">
+      <c r="N106" s="5">
         <v>103</v>
       </c>
-      <c r="O106" s="28">
+      <c r="O106" s="27">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="P106" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q106" s="6"/>
-      <c r="R106" s="6">
+      <c r="P106" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q106" s="5">
+        <v>0</v>
+      </c>
+      <c r="R106" s="5">
         <f t="shared" si="8"/>
-        <v>97</v>
-      </c>
-      <c r="S106" s="16">
+        <v>39</v>
+      </c>
+      <c r="S106" s="15">
         <f t="shared" si="7"/>
         <v>46166</v>
       </c>
     </row>
     <row r="107" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N107" s="6">
+      <c r="N107" s="5">
         <v>104</v>
       </c>
-      <c r="O107" s="28">
+      <c r="O107" s="27">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="P107" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q107" s="6"/>
-      <c r="R107" s="6">
+      <c r="P107" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q107" s="5">
+        <v>0</v>
+      </c>
+      <c r="R107" s="5">
         <f t="shared" si="8"/>
-        <v>97</v>
-      </c>
-      <c r="S107" s="16">
+        <v>39</v>
+      </c>
+      <c r="S107" s="15">
         <f t="shared" si="7"/>
         <v>46167</v>
       </c>
     </row>
     <row r="108" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N108" s="6">
+      <c r="N108" s="5">
         <v>105</v>
       </c>
-      <c r="O108" s="28">
+      <c r="O108" s="27">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="P108" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q108" s="6"/>
-      <c r="R108" s="6">
+      <c r="P108" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q108" s="5">
+        <v>0</v>
+      </c>
+      <c r="R108" s="5">
         <f t="shared" si="8"/>
-        <v>97</v>
-      </c>
-      <c r="S108" s="16">
+        <v>39</v>
+      </c>
+      <c r="S108" s="15">
         <f t="shared" si="7"/>
         <v>46168</v>
       </c>
     </row>
     <row r="109" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N109" s="6">
+      <c r="N109" s="5">
         <v>106</v>
       </c>
-      <c r="O109" s="28">
+      <c r="O109" s="27">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="P109" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q109" s="6"/>
-      <c r="R109" s="6">
+      <c r="P109" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q109" s="5">
+        <v>0</v>
+      </c>
+      <c r="R109" s="5">
         <f t="shared" si="8"/>
-        <v>97</v>
-      </c>
-      <c r="S109" s="16">
+        <v>39</v>
+      </c>
+      <c r="S109" s="15">
         <f t="shared" si="7"/>
         <v>46169</v>
       </c>
     </row>
     <row r="110" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N110" s="6">
+      <c r="N110" s="5">
         <v>107</v>
       </c>
-      <c r="O110" s="28">
+      <c r="O110" s="27">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="P110" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q110" s="6"/>
-      <c r="R110" s="6">
+      <c r="P110" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q110" s="5">
+        <v>13</v>
+      </c>
+      <c r="R110" s="5">
         <f t="shared" si="8"/>
-        <v>97</v>
-      </c>
-      <c r="S110" s="16">
+        <v>26</v>
+      </c>
+      <c r="S110" s="15">
         <f t="shared" si="7"/>
         <v>46170</v>
       </c>
     </row>
     <row r="111" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N111" s="6">
+      <c r="N111" s="5">
         <v>108</v>
       </c>
-      <c r="O111" s="28">
+      <c r="O111" s="27">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="P111" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q111" s="6"/>
-      <c r="R111" s="6">
+      <c r="P111" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q111" s="5">
+        <v>0</v>
+      </c>
+      <c r="R111" s="5">
         <f t="shared" si="8"/>
-        <v>97</v>
-      </c>
-      <c r="S111" s="16">
+        <v>26</v>
+      </c>
+      <c r="S111" s="15">
         <f t="shared" si="7"/>
         <v>46171</v>
       </c>
     </row>
     <row r="112" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N112" s="6">
+      <c r="N112" s="5">
         <v>109</v>
       </c>
-      <c r="O112" s="28">
+      <c r="O112" s="27">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="P112" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q112" s="6"/>
-      <c r="R112" s="6">
+      <c r="P112" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q112" s="5">
+        <v>0</v>
+      </c>
+      <c r="R112" s="5">
         <f t="shared" si="8"/>
-        <v>97</v>
-      </c>
-      <c r="S112" s="16">
+        <v>26</v>
+      </c>
+      <c r="S112" s="15">
         <f t="shared" si="7"/>
         <v>46172</v>
       </c>
     </row>
     <row r="113" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N113" s="6">
+      <c r="N113" s="5">
         <v>110</v>
       </c>
-      <c r="O113" s="28">
+      <c r="O113" s="27">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="P113" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q113" s="6"/>
-      <c r="R113" s="6">
+      <c r="P113" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q113" s="5">
+        <v>0</v>
+      </c>
+      <c r="R113" s="5">
         <f t="shared" si="8"/>
-        <v>97</v>
-      </c>
-      <c r="S113" s="16">
+        <v>26</v>
+      </c>
+      <c r="S113" s="15">
         <f t="shared" si="7"/>
         <v>46173</v>
       </c>
     </row>
     <row r="114" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N114" s="6">
+      <c r="N114" s="5">
         <v>111</v>
       </c>
-      <c r="O114" s="28">
+      <c r="O114" s="27">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="P114" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q114" s="6"/>
-      <c r="R114" s="6">
+      <c r="P114" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q114" s="5">
+        <v>0</v>
+      </c>
+      <c r="R114" s="5">
         <f t="shared" si="8"/>
-        <v>97</v>
-      </c>
-      <c r="S114" s="16">
+        <v>26</v>
+      </c>
+      <c r="S114" s="15">
         <f t="shared" si="7"/>
         <v>46174</v>
       </c>
     </row>
     <row r="115" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N115" s="6">
+      <c r="N115" s="5">
         <v>112</v>
       </c>
-      <c r="O115" s="28">
+      <c r="O115" s="27">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="P115" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q115" s="6"/>
-      <c r="R115" s="6">
+      <c r="P115" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q115" s="5">
+        <v>0</v>
+      </c>
+      <c r="R115" s="5">
         <f t="shared" si="8"/>
-        <v>97</v>
-      </c>
-      <c r="S115" s="16">
+        <v>26</v>
+      </c>
+      <c r="S115" s="15">
         <f t="shared" si="7"/>
         <v>46175</v>
       </c>
     </row>
     <row r="116" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N116" s="6">
+      <c r="N116" s="5">
         <v>113</v>
       </c>
-      <c r="O116" s="28">
+      <c r="O116" s="27">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="P116" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q116" s="6"/>
-      <c r="R116" s="6">
+      <c r="P116" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q116" s="5">
+        <v>21</v>
+      </c>
+      <c r="R116" s="5">
         <f t="shared" si="8"/>
-        <v>97</v>
-      </c>
-      <c r="S116" s="16">
+        <v>5</v>
+      </c>
+      <c r="S116" s="15">
         <f t="shared" si="7"/>
         <v>46176</v>
       </c>
     </row>
     <row r="117" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="N117" s="6">
+      <c r="N117" s="5">
         <v>114</v>
       </c>
-      <c r="O117" s="28">
+      <c r="O117" s="27">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="P117" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q117" s="6"/>
-      <c r="R117" s="6">
+      <c r="P117" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q117" s="5">
+        <v>5</v>
+      </c>
+      <c r="R117" s="5">
         <f t="shared" si="8"/>
-        <v>97</v>
-      </c>
-      <c r="S117" s="16">
+        <v>0</v>
+      </c>
+      <c r="S117" s="15">
         <f t="shared" si="7"/>
         <v>46177</v>
       </c>
     </row>
     <row r="118" spans="14:19" x14ac:dyDescent="0.25">
-      <c r="S118" s="5"/>
+      <c r="N118" s="5">
+        <v>115</v>
+      </c>
+      <c r="O118" s="27">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="P118" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q118" s="5">
+        <v>0</v>
+      </c>
+      <c r="R118" s="5">
+        <f t="shared" ref="R118:R122" si="10">IF(Q118&lt;&gt;"",R117-Q118,R117)</f>
+        <v>0</v>
+      </c>
+      <c r="S118" s="15">
+        <f t="shared" si="7"/>
+        <v>46178</v>
+      </c>
+    </row>
+    <row r="119" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N119" s="5">
+        <v>116</v>
+      </c>
+      <c r="O119" s="27">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="P119" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q119" s="5">
+        <v>0</v>
+      </c>
+      <c r="R119" s="5">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="S119" s="15">
+        <f t="shared" si="7"/>
+        <v>46179</v>
+      </c>
+    </row>
+    <row r="120" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N120" s="5">
+        <v>117</v>
+      </c>
+      <c r="O120" s="27">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="P120" s="5">
+        <v>3</v>
+      </c>
+      <c r="Q120" s="5">
+        <v>0</v>
+      </c>
+      <c r="R120" s="5">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="S120" s="15">
+        <f t="shared" si="7"/>
+        <v>46180</v>
+      </c>
+    </row>
+    <row r="121" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N121" s="5">
+        <v>118</v>
+      </c>
+      <c r="O121" s="27">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="P121" s="5">
+        <v>4</v>
+      </c>
+      <c r="Q121" s="5">
+        <v>0</v>
+      </c>
+      <c r="R121" s="5">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="S121" s="15">
+        <f t="shared" si="7"/>
+        <v>46181</v>
+      </c>
+    </row>
+    <row r="122" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N122" s="5">
+        <v>119</v>
+      </c>
+      <c r="O122" s="27">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="P122" s="5">
+        <v>5</v>
+      </c>
+      <c r="Q122" s="5">
+        <v>0</v>
+      </c>
+      <c r="R122" s="5">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="S122" s="15">
+        <f t="shared" si="7"/>
+        <v>46182</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="N3:N117">
+  <conditionalFormatting sqref="N3:N122">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -6505,7 +6811,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P3:P117">
+  <conditionalFormatting sqref="P3:P122">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -6517,7 +6823,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q3:Q117">
+  <conditionalFormatting sqref="Q3:Q122">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -6529,7 +6835,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R3:R117">
+  <conditionalFormatting sqref="R3:R122">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -6559,10 +6865,10 @@
   </cols>
   <sheetData>
     <row r="6" spans="6:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="F6" s="22" t="s">
+      <c r="F6" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="3">
         <v>3</v>
       </c>
       <c r="J6" s="1" t="s">
@@ -6591,470 +6897,470 @@
       </c>
     </row>
     <row r="7" spans="6:17" x14ac:dyDescent="0.25">
-      <c r="F7" s="23" t="s">
+      <c r="F7" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="3">
         <v>5</v>
       </c>
-      <c r="J7" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="K7" s="17" t="s">
+      <c r="J7" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="K7" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="L7" s="19" t="s">
+      <c r="L7" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="M7" s="22" t="s">
+      <c r="M7" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="N7" s="22">
-        <v>3</v>
-      </c>
-      <c r="O7" s="20">
-        <v>3</v>
-      </c>
-      <c r="P7" s="23" t="s">
+      <c r="N7" s="21">
+        <v>3</v>
+      </c>
+      <c r="O7" s="19">
+        <v>3</v>
+      </c>
+      <c r="P7" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="Q7" s="4" t="s">
+      <c r="Q7" s="3" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="8" spans="6:17" x14ac:dyDescent="0.25">
-      <c r="F8" s="24" t="s">
+      <c r="F8" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="3">
         <v>8</v>
       </c>
-      <c r="J8" s="18" t="s">
+      <c r="J8" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="K8" s="17" t="s">
+      <c r="K8" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="L8" s="20" t="s">
+      <c r="L8" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="M8" s="24" t="s">
+      <c r="M8" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="N8" s="24">
+      <c r="N8" s="23">
         <v>8</v>
       </c>
-      <c r="O8" s="19">
+      <c r="O8" s="18">
         <v>1</v>
       </c>
-      <c r="P8" s="23" t="s">
+      <c r="P8" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="Q8" s="4" t="s">
+      <c r="Q8" s="3" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="9" spans="6:17" x14ac:dyDescent="0.25">
-      <c r="F9" s="26" t="s">
+      <c r="F9" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G9" s="3">
         <v>13</v>
       </c>
-      <c r="J9" s="18" t="s">
+      <c r="J9" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="K9" s="17" t="s">
+      <c r="K9" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="L9" s="20" t="s">
+      <c r="L9" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="M9" s="26" t="s">
+      <c r="M9" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="N9" s="26">
+      <c r="N9" s="25">
         <v>13</v>
       </c>
-      <c r="O9" s="19">
+      <c r="O9" s="18">
         <v>1</v>
       </c>
-      <c r="P9" s="23" t="s">
+      <c r="P9" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="Q9" s="4" t="s">
+      <c r="Q9" s="3" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="10" spans="6:17" x14ac:dyDescent="0.25">
-      <c r="F10" s="25" t="s">
+      <c r="F10" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G10" s="3">
         <v>21</v>
       </c>
-      <c r="J10" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="K10" s="17" t="s">
+      <c r="J10" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="K10" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="L10" s="20" t="s">
+      <c r="L10" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="M10" s="26" t="s">
+      <c r="M10" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="N10" s="26">
+      <c r="N10" s="25">
         <v>13</v>
       </c>
-      <c r="O10" s="19">
+      <c r="O10" s="18">
         <v>1</v>
       </c>
-      <c r="P10" s="23" t="s">
+      <c r="P10" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="Q10" s="4" t="s">
+      <c r="Q10" s="3" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="11" spans="6:17" x14ac:dyDescent="0.25">
-      <c r="J11" s="18" t="s">
+      <c r="J11" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="K11" s="17" t="s">
+      <c r="K11" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="L11" s="19" t="s">
+      <c r="L11" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="M11" s="26" t="s">
+      <c r="M11" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="N11" s="26">
+      <c r="N11" s="25">
         <v>13</v>
       </c>
-      <c r="O11" s="21">
+      <c r="O11" s="20">
         <v>2</v>
       </c>
-      <c r="P11" s="23" t="s">
+      <c r="P11" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="Q11" s="4" t="s">
+      <c r="Q11" s="3" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="12" spans="6:17" x14ac:dyDescent="0.25">
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="5">
         <f>SUM(N7:N22)</f>
         <v>113</v>
       </c>
-      <c r="J12" s="18" t="s">
+      <c r="J12" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="K12" s="17" t="s">
+      <c r="K12" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="L12" s="20" t="s">
+      <c r="L12" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="M12" s="24" t="s">
+      <c r="M12" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="N12" s="24">
+      <c r="N12" s="23">
         <v>8</v>
       </c>
-      <c r="O12" s="19">
+      <c r="O12" s="18">
         <v>1</v>
       </c>
-      <c r="P12" s="23" t="s">
+      <c r="P12" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="Q12" s="4" t="s">
+      <c r="Q12" s="3" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="13" spans="6:17" x14ac:dyDescent="0.25">
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="G13" s="6">
-        <v>114</v>
-      </c>
-      <c r="J13" s="18" t="s">
+      <c r="G13" s="5">
+        <v>119</v>
+      </c>
+      <c r="J13" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="K13" s="17" t="s">
+      <c r="K13" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="L13" s="19" t="s">
+      <c r="L13" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="M13" s="23" t="s">
+      <c r="M13" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="N13" s="23">
+      <c r="N13" s="22">
         <v>5</v>
       </c>
-      <c r="O13" s="21">
+      <c r="O13" s="20">
         <v>2</v>
       </c>
-      <c r="P13" s="23" t="s">
+      <c r="P13" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="Q13" s="4" t="s">
+      <c r="Q13" s="3" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="14" spans="6:17" x14ac:dyDescent="0.25">
-      <c r="F14" s="10" t="s">
+      <c r="F14" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G14" s="5">
         <f>ROUNDUP(G12/G13, 0)</f>
         <v>1</v>
       </c>
-      <c r="J14" s="18" t="s">
+      <c r="J14" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="K14" s="17" t="s">
+      <c r="K14" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="L14" s="19" t="s">
+      <c r="L14" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="M14" s="22" t="s">
+      <c r="M14" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="N14" s="22">
-        <v>3</v>
-      </c>
-      <c r="O14" s="20">
-        <v>3</v>
-      </c>
-      <c r="P14" s="23" t="s">
+      <c r="N14" s="21">
+        <v>3</v>
+      </c>
+      <c r="O14" s="19">
+        <v>3</v>
+      </c>
+      <c r="P14" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="Q14" s="4" t="s">
+      <c r="Q14" s="3" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="15" spans="6:17" x14ac:dyDescent="0.25">
-      <c r="F15" s="29" t="s">
+      <c r="F15" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="J15" s="18" t="s">
+      <c r="J15" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="K15" s="17" t="s">
+      <c r="K15" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="L15" s="20" t="s">
+      <c r="L15" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="M15" s="26" t="s">
+      <c r="M15" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="N15" s="26">
+      <c r="N15" s="25">
         <v>13</v>
       </c>
-      <c r="O15" s="19">
+      <c r="O15" s="18">
         <v>1</v>
       </c>
-      <c r="P15" s="23" t="s">
+      <c r="P15" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="Q15" s="4" t="s">
+      <c r="Q15" s="3" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="16" spans="6:17" x14ac:dyDescent="0.25">
-      <c r="J16" s="18" t="s">
+      <c r="J16" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="K16" s="17" t="s">
+      <c r="K16" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L16" s="20" t="s">
+      <c r="L16" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="M16" s="24" t="s">
+      <c r="M16" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="N16" s="24">
+      <c r="N16" s="23">
         <v>8</v>
       </c>
-      <c r="O16" s="19">
+      <c r="O16" s="18">
         <v>1</v>
       </c>
-      <c r="P16" s="23" t="s">
+      <c r="P16" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="Q16" s="4" t="s">
+      <c r="Q16" s="3" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="17" spans="6:17" x14ac:dyDescent="0.25">
-      <c r="F17" s="5"/>
-      <c r="J17" s="18" t="s">
+      <c r="F17" s="4"/>
+      <c r="J17" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="K17" s="17" t="s">
+      <c r="K17" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="L17" s="19" t="s">
+      <c r="L17" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="M17" s="23" t="s">
+      <c r="M17" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="N17" s="23">
+      <c r="N17" s="22">
         <v>5</v>
       </c>
-      <c r="O17" s="21">
+      <c r="O17" s="20">
         <v>2</v>
       </c>
-      <c r="P17" s="23" t="s">
+      <c r="P17" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="Q17" s="4" t="s">
+      <c r="Q17" s="3" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="18" spans="6:17" x14ac:dyDescent="0.25">
-      <c r="F18" s="5"/>
-      <c r="J18" s="18" t="s">
+      <c r="F18" s="4"/>
+      <c r="J18" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="K18" s="17" t="s">
+      <c r="K18" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="L18" s="19" t="s">
+      <c r="L18" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="M18" s="23" t="s">
+      <c r="M18" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="N18" s="23">
+      <c r="N18" s="22">
         <v>5</v>
       </c>
-      <c r="O18" s="21">
+      <c r="O18" s="20">
         <v>2</v>
       </c>
-      <c r="P18" s="23" t="s">
+      <c r="P18" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="Q18" s="4" t="s">
+      <c r="Q18" s="3" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="19" spans="6:17" x14ac:dyDescent="0.25">
-      <c r="J19" s="18" t="s">
+      <c r="J19" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="K19" s="17" t="s">
+      <c r="K19" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="L19" s="19" t="s">
+      <c r="L19" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="M19" s="22" t="s">
+      <c r="M19" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="N19" s="22">
-        <v>3</v>
-      </c>
-      <c r="O19" s="20">
-        <v>3</v>
-      </c>
-      <c r="P19" s="23" t="s">
+      <c r="N19" s="21">
+        <v>3</v>
+      </c>
+      <c r="O19" s="19">
+        <v>3</v>
+      </c>
+      <c r="P19" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="Q19" s="4" t="s">
+      <c r="Q19" s="3" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="20" spans="6:17" x14ac:dyDescent="0.25">
-      <c r="J20" s="18" t="s">
+      <c r="J20" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="K20" s="17" t="s">
+      <c r="K20" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="L20" s="19" t="s">
+      <c r="L20" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="M20" s="23" t="s">
+      <c r="M20" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="N20" s="23">
+      <c r="N20" s="22">
         <v>5</v>
       </c>
-      <c r="O20" s="20">
-        <v>3</v>
-      </c>
-      <c r="P20" s="23" t="s">
+      <c r="O20" s="19">
+        <v>3</v>
+      </c>
+      <c r="P20" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="Q20" s="4" t="s">
+      <c r="Q20" s="3" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="21" spans="6:17" x14ac:dyDescent="0.25">
-      <c r="J21" s="18" t="s">
+      <c r="J21" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="K21" s="17" t="s">
+      <c r="K21" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="L21" s="20" t="s">
+      <c r="L21" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="M21" s="22" t="s">
+      <c r="M21" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="N21" s="22">
-        <v>3</v>
-      </c>
-      <c r="O21" s="19">
+      <c r="N21" s="21">
+        <v>3</v>
+      </c>
+      <c r="O21" s="18">
         <v>1</v>
       </c>
-      <c r="P21" s="23" t="s">
+      <c r="P21" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="Q21" s="4" t="s">
+      <c r="Q21" s="3" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="22" spans="6:17" x14ac:dyDescent="0.25">
-      <c r="J22" s="18" t="s">
+      <c r="J22" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="K22" s="17" t="s">
+      <c r="K22" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="L22" s="20" t="s">
+      <c r="L22" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="M22" s="23" t="s">
+      <c r="M22" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="N22" s="23">
+      <c r="N22" s="22">
         <v>5</v>
       </c>
-      <c r="O22" s="19">
+      <c r="O22" s="18">
         <v>1</v>
       </c>
-      <c r="P22" s="23" t="s">
+      <c r="P22" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="Q22" s="4" t="s">
+      <c r="Q22" s="3" t="s">
         <v>67</v>
       </c>
     </row>
@@ -7077,10 +7383,10 @@
   </cols>
   <sheetData>
     <row r="6" spans="6:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="F6" s="22" t="s">
+      <c r="F6" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="3">
         <v>3</v>
       </c>
       <c r="J6" s="1" t="s">
@@ -7109,472 +7415,764 @@
       </c>
     </row>
     <row r="7" spans="6:17" x14ac:dyDescent="0.25">
-      <c r="F7" s="23" t="s">
+      <c r="F7" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="3">
         <v>5</v>
       </c>
-      <c r="J7" s="18" t="s">
+      <c r="J7" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="K7" s="17" t="s">
+      <c r="K7" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="L7" s="19" t="s">
+      <c r="L7" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="M7" s="22" t="s">
+      <c r="M7" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="N7" s="22">
-        <v>3</v>
-      </c>
-      <c r="O7" s="21">
+      <c r="N7" s="21">
+        <v>3</v>
+      </c>
+      <c r="O7" s="20">
         <v>2</v>
       </c>
-      <c r="P7" s="19" t="s">
+      <c r="P7" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="Q7" s="4" t="s">
+      <c r="Q7" s="3" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="8" spans="6:17" x14ac:dyDescent="0.25">
-      <c r="F8" s="24" t="s">
+      <c r="F8" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="3">
         <v>8</v>
       </c>
-      <c r="J8" s="18" t="s">
+      <c r="J8" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="K8" s="17" t="s">
+      <c r="K8" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="L8" s="19" t="s">
+      <c r="L8" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="M8" s="22" t="s">
+      <c r="M8" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="N8" s="22">
-        <v>3</v>
-      </c>
-      <c r="O8" s="21">
+      <c r="N8" s="21">
+        <v>3</v>
+      </c>
+      <c r="O8" s="20">
         <v>2</v>
       </c>
-      <c r="P8" s="19" t="s">
+      <c r="P8" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="Q8" s="4" t="s">
+      <c r="Q8" s="3" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="9" spans="6:17" x14ac:dyDescent="0.25">
-      <c r="F9" s="26" t="s">
+      <c r="F9" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G9" s="3">
         <v>13</v>
       </c>
-      <c r="J9" s="18" t="s">
+      <c r="J9" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="K9" s="17" t="s">
+      <c r="K9" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="L9" s="21" t="s">
+      <c r="L9" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="M9" s="24" t="s">
+      <c r="M9" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="N9" s="24">
+      <c r="N9" s="23">
         <v>8</v>
       </c>
-      <c r="O9" s="20">
-        <v>3</v>
-      </c>
-      <c r="P9" s="19" t="s">
+      <c r="O9" s="19">
+        <v>3</v>
+      </c>
+      <c r="P9" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="Q9" s="4" t="s">
+      <c r="Q9" s="3" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="10" spans="6:17" x14ac:dyDescent="0.25">
-      <c r="F10" s="25" t="s">
+      <c r="F10" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G10" s="3">
         <v>21</v>
       </c>
-      <c r="J10" s="18" t="s">
+      <c r="J10" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="K10" s="17" t="s">
+      <c r="K10" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="L10" s="19" t="s">
+      <c r="L10" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="M10" s="26" t="s">
+      <c r="M10" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="N10" s="26">
+      <c r="N10" s="25">
         <v>13</v>
       </c>
-      <c r="O10" s="19">
+      <c r="O10" s="18">
         <v>1</v>
       </c>
-      <c r="P10" s="19" t="s">
+      <c r="P10" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="Q10" s="4" t="s">
+      <c r="Q10" s="3" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="11" spans="6:17" x14ac:dyDescent="0.25">
-      <c r="J11" s="18" t="s">
+      <c r="J11" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="K11" s="43" t="s">
+      <c r="K11" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="L11" s="19" t="s">
+      <c r="L11" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="M11" s="26" t="s">
+      <c r="M11" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="N11" s="26">
+      <c r="N11" s="25">
         <v>13</v>
       </c>
-      <c r="O11" s="19">
+      <c r="O11" s="18">
         <v>1</v>
       </c>
-      <c r="P11" s="19" t="s">
+      <c r="P11" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="Q11" s="4" t="s">
+      <c r="Q11" s="3" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="12" spans="6:17" x14ac:dyDescent="0.25">
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="5">
         <f>SUM(N7:N22)</f>
         <v>101</v>
       </c>
-      <c r="J12" s="18" t="s">
+      <c r="J12" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="K12" s="17" t="s">
+      <c r="K12" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="L12" s="20" t="s">
+      <c r="L12" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="M12" s="24" t="s">
+      <c r="M12" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="N12" s="24">
+      <c r="N12" s="23">
         <v>8</v>
       </c>
-      <c r="O12" s="21">
+      <c r="O12" s="20">
         <v>2</v>
       </c>
-      <c r="P12" s="19" t="s">
+      <c r="P12" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="Q12" s="4" t="s">
+      <c r="Q12" s="3" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="13" spans="6:17" x14ac:dyDescent="0.25">
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="G13" s="6">
-        <v>114</v>
-      </c>
-      <c r="J13" s="18" t="s">
+      <c r="G13" s="5">
+        <v>119</v>
+      </c>
+      <c r="J13" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="K13" s="43" t="s">
+      <c r="K13" s="40" t="s">
         <v>74</v>
       </c>
-      <c r="L13" s="20" t="s">
+      <c r="L13" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="M13" s="24" t="s">
+      <c r="M13" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="N13" s="24">
+      <c r="N13" s="23">
         <v>8</v>
       </c>
-      <c r="O13" s="21">
+      <c r="O13" s="20">
         <v>2</v>
       </c>
-      <c r="P13" s="19" t="s">
+      <c r="P13" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="Q13" s="4" t="s">
+      <c r="Q13" s="3" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="14" spans="6:17" x14ac:dyDescent="0.25">
-      <c r="F14" s="10" t="s">
+      <c r="F14" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G14" s="5">
         <f>ROUNDUP(G12/G13, 0)</f>
         <v>1</v>
       </c>
-      <c r="J14" s="18" t="s">
+      <c r="J14" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="K14" s="43" t="s">
+      <c r="K14" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="L14" s="20" t="s">
+      <c r="L14" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="M14" s="22" t="s">
+      <c r="M14" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="N14" s="22">
-        <v>3</v>
-      </c>
-      <c r="O14" s="20">
-        <v>3</v>
-      </c>
-      <c r="P14" s="19" t="s">
+      <c r="N14" s="21">
+        <v>3</v>
+      </c>
+      <c r="O14" s="19">
+        <v>3</v>
+      </c>
+      <c r="P14" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="Q14" s="4" t="s">
+      <c r="Q14" s="3" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="15" spans="6:17" x14ac:dyDescent="0.25">
-      <c r="F15" s="29" t="s">
+      <c r="F15" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="J15" s="18" t="s">
+      <c r="J15" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="K15" s="17" t="s">
+      <c r="K15" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="L15" s="20" t="s">
+      <c r="L15" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="M15" s="23" t="s">
+      <c r="M15" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="N15" s="23">
+      <c r="N15" s="22">
         <v>5</v>
       </c>
-      <c r="O15" s="20">
-        <v>3</v>
-      </c>
-      <c r="P15" s="19" t="s">
+      <c r="O15" s="19">
+        <v>3</v>
+      </c>
+      <c r="P15" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="Q15" s="4" t="s">
+      <c r="Q15" s="3" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="16" spans="6:17" x14ac:dyDescent="0.25">
-      <c r="J16" s="18" t="s">
+      <c r="J16" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="K16" s="17" t="s">
+      <c r="K16" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="L16" s="20" t="s">
+      <c r="L16" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="M16" s="24" t="s">
+      <c r="M16" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="N16" s="24">
+      <c r="N16" s="23">
         <v>8</v>
       </c>
-      <c r="O16" s="19">
+      <c r="O16" s="18">
         <v>1</v>
       </c>
-      <c r="P16" s="19" t="s">
+      <c r="P16" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="Q16" s="4" t="s">
+      <c r="Q16" s="3" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="17" spans="6:17" x14ac:dyDescent="0.25">
-      <c r="F17" s="5"/>
-      <c r="J17" s="18" t="s">
+      <c r="F17" s="4"/>
+      <c r="J17" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="K17" s="17" t="s">
+      <c r="K17" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="L17" s="19" t="s">
+      <c r="L17" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="M17" s="24" t="s">
+      <c r="M17" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="N17" s="24">
+      <c r="N17" s="23">
         <v>8</v>
       </c>
-      <c r="O17" s="21">
+      <c r="O17" s="20">
         <v>2</v>
       </c>
-      <c r="P17" s="19" t="s">
+      <c r="P17" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="Q17" s="4" t="s">
+      <c r="Q17" s="3" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="18" spans="6:17" x14ac:dyDescent="0.25">
-      <c r="F18" s="5"/>
-      <c r="J18" s="18" t="s">
+      <c r="F18" s="4"/>
+      <c r="J18" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="K18" s="17" t="s">
+      <c r="K18" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="L18" s="20" t="s">
+      <c r="L18" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="M18" s="23" t="s">
+      <c r="M18" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="N18" s="23">
+      <c r="N18" s="22">
         <v>5</v>
       </c>
-      <c r="O18" s="19">
+      <c r="O18" s="18">
         <v>1</v>
       </c>
-      <c r="P18" s="19" t="s">
+      <c r="P18" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="Q18" s="4" t="s">
+      <c r="Q18" s="3" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="19" spans="6:17" x14ac:dyDescent="0.25">
-      <c r="J19" s="18" t="s">
+      <c r="J19" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="K19" s="17" t="s">
+      <c r="K19" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="L19" s="20" t="s">
+      <c r="L19" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="M19" s="23" t="s">
+      <c r="M19" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="N19" s="23">
+      <c r="N19" s="22">
         <v>5</v>
       </c>
-      <c r="O19" s="19">
+      <c r="O19" s="18">
         <v>1</v>
       </c>
-      <c r="P19" s="19" t="s">
+      <c r="P19" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="Q19" s="4" t="s">
+      <c r="Q19" s="3" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="20" spans="6:17" x14ac:dyDescent="0.25">
-      <c r="J20" s="18" t="s">
+      <c r="J20" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="K20" s="17" t="s">
+      <c r="K20" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="L20" s="20" t="s">
+      <c r="L20" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="M20" s="23" t="s">
+      <c r="M20" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="N20" s="23">
+      <c r="N20" s="22">
         <v>5</v>
       </c>
-      <c r="O20" s="20">
-        <v>3</v>
-      </c>
-      <c r="P20" s="19" t="s">
+      <c r="O20" s="19">
+        <v>3</v>
+      </c>
+      <c r="P20" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="Q20" s="4" t="s">
+      <c r="Q20" s="3" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="21" spans="6:17" x14ac:dyDescent="0.25">
-      <c r="J21" s="18" t="s">
+      <c r="J21" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="K21" s="43" t="s">
+      <c r="K21" s="40" t="s">
         <v>86</v>
       </c>
-      <c r="L21" s="20" t="s">
+      <c r="L21" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="M21" s="22" t="s">
+      <c r="M21" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="N21" s="22">
-        <v>3</v>
-      </c>
-      <c r="O21" s="20">
-        <v>3</v>
-      </c>
-      <c r="P21" s="19" t="s">
+      <c r="N21" s="21">
+        <v>3</v>
+      </c>
+      <c r="O21" s="19">
+        <v>3</v>
+      </c>
+      <c r="P21" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="Q21" s="4" t="s">
+      <c r="Q21" s="3" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="22" spans="6:17" x14ac:dyDescent="0.25">
-      <c r="J22" s="18" t="s">
+      <c r="J22" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="K22" s="43" t="s">
+      <c r="K22" s="40" t="s">
         <v>87</v>
       </c>
-      <c r="L22" s="19" t="s">
+      <c r="L22" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="M22" s="22" t="s">
+      <c r="M22" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="N22" s="22">
-        <v>3</v>
-      </c>
-      <c r="O22" s="19">
+      <c r="N22" s="21">
+        <v>3</v>
+      </c>
+      <c r="O22" s="18">
         <v>1</v>
       </c>
-      <c r="P22" s="19" t="s">
+      <c r="P22" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="Q22" s="4" t="s">
+      <c r="Q22" s="3" t="s">
         <v>67</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95B03FC2-15AB-485F-987B-F9EE5E655707}">
+  <dimension ref="F6:Q18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="6" max="6" width="36.28515625" customWidth="1"/>
+    <col min="7" max="7" width="19" customWidth="1"/>
+    <col min="10" max="10" width="41.42578125" customWidth="1"/>
+    <col min="11" max="11" width="45.28515625" customWidth="1"/>
+    <col min="12" max="12" width="28.28515625" customWidth="1"/>
+    <col min="17" max="17" width="13" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="6" spans="6:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F6" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="G6" s="3">
+        <v>3</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="6:17" x14ac:dyDescent="0.25">
+      <c r="F7" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="G7" s="3">
+        <v>5</v>
+      </c>
+      <c r="J7" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="K7" s="40" t="s">
+        <v>95</v>
+      </c>
+      <c r="L7" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="M7" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="N7" s="25">
+        <v>13</v>
+      </c>
+      <c r="O7" s="20">
+        <v>2</v>
+      </c>
+      <c r="P7" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="6:17" x14ac:dyDescent="0.25">
+      <c r="F8" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="G8" s="3">
+        <v>8</v>
+      </c>
+      <c r="J8" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="K8" s="40" t="s">
+        <v>96</v>
+      </c>
+      <c r="L8" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="M8" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="N8" s="24">
+        <v>21</v>
+      </c>
+      <c r="O8" s="19">
+        <v>3</v>
+      </c>
+      <c r="P8" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="6:17" x14ac:dyDescent="0.25">
+      <c r="F9" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="G9" s="3">
+        <v>13</v>
+      </c>
+      <c r="J9" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="K9" s="40" t="s">
+        <v>97</v>
+      </c>
+      <c r="L9" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="M9" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="N9" s="23">
+        <v>8</v>
+      </c>
+      <c r="O9" s="20">
+        <v>2</v>
+      </c>
+      <c r="P9" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="6:17" x14ac:dyDescent="0.25">
+      <c r="F10" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="G10" s="3">
+        <v>21</v>
+      </c>
+      <c r="J10" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="K10" s="40" t="s">
+        <v>98</v>
+      </c>
+      <c r="L10" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="M10" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="N10" s="23">
+        <v>8</v>
+      </c>
+      <c r="O10" s="18">
+        <v>1</v>
+      </c>
+      <c r="P10" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="6:17" x14ac:dyDescent="0.25">
+      <c r="J11" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="K11" s="41" t="s">
+        <v>99</v>
+      </c>
+      <c r="L11" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="M11" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="N11" s="32">
+        <v>8</v>
+      </c>
+      <c r="O11" s="33">
+        <v>2</v>
+      </c>
+      <c r="P11" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q11" s="35" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="6:17" x14ac:dyDescent="0.25">
+      <c r="F12" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="G12" s="5" t="e">
+        <f>SUM(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J12" s="30" t="s">
+        <v>116</v>
+      </c>
+      <c r="K12" s="42" t="s">
+        <v>117</v>
+      </c>
+      <c r="L12" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="M12" s="37" t="s">
+        <v>64</v>
+      </c>
+      <c r="N12" s="37">
+        <v>21</v>
+      </c>
+      <c r="O12" s="11">
+        <v>1</v>
+      </c>
+      <c r="P12" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q12" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="6:17" x14ac:dyDescent="0.25">
+      <c r="F13" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="G13" s="5">
+        <v>119</v>
+      </c>
+      <c r="J13" s="30" t="s">
+        <v>118</v>
+      </c>
+      <c r="K13" s="42" t="s">
+        <v>119</v>
+      </c>
+      <c r="L13" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="M13" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="N13" s="38">
+        <v>13</v>
+      </c>
+      <c r="O13" s="39">
+        <v>2</v>
+      </c>
+      <c r="P13" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q13" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="6:17" x14ac:dyDescent="0.25">
+      <c r="F14" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="G14" s="5" t="e">
+        <f>ROUNDUP(G12/G13, 0)</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="15" spans="6:17" x14ac:dyDescent="0.25">
+      <c r="F15" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F18" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
